--- a/docs/xlsx/jobs-2026-09-29.xlsx
+++ b/docs/xlsx/jobs-2026-09-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="590">
   <si>
     <t>Title</t>
   </si>
@@ -40,6 +40,993 @@
     <t>Link</t>
   </si>
   <si>
+    <t>Animal Care Specialist (Herps)</t>
+  </si>
+  <si>
+    <t>Tree Frog Treks</t>
+  </si>
+  <si>
+    <t>San Francisco, CA</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$30 - $32 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-animal-care-specialist-herps-san-francisco-california/4907508641</t>
+  </si>
+  <si>
+    <t>Arizona – New Mexico Director</t>
+  </si>
+  <si>
+    <t>Western Watersheds Project</t>
+  </si>
+  <si>
+    <t>Tucson, AZ</t>
+  </si>
+  <si>
+    <t>$84,916 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-arizona--new-mexico-director-tucson-arizona/9917645507</t>
+  </si>
+  <si>
+    <t>Associate Project Manager or Project Manager</t>
+  </si>
+  <si>
+    <t>San Francisco Estuary Institute</t>
+  </si>
+  <si>
+    <t>Richmond, CA</t>
+  </si>
+  <si>
+    <t>$92,750 - $110,500 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-associate-project-manager-or-project-manager-richmond-california/1427524941</t>
+  </si>
+  <si>
+    <t>Attorney Supervisor</t>
+  </si>
+  <si>
+    <t>California State Water Resources Control Board</t>
+  </si>
+  <si>
+    <t>Sacramento, CA</t>
+  </si>
+  <si>
+    <t>$12,590 - $16,900 per month</t>
+  </si>
+  <si>
+    <t>hydrology-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-attorney-supervisor-sacramento-california/2637894484</t>
+  </si>
+  <si>
+    <t>Bookkeeper</t>
+  </si>
+  <si>
+    <t>McKenzie River Trust</t>
+  </si>
+  <si>
+    <t>Eugene, OR</t>
+  </si>
+  <si>
+    <t>$65,000 - $75,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-bookkeeper-eugene-oregon/9553788031</t>
+  </si>
+  <si>
+    <t>Chesapeake Gateways Ambassador</t>
+  </si>
+  <si>
+    <t>Appalachian Conservation Corps and the National Park Service</t>
+  </si>
+  <si>
+    <t>Triangle, VA</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$760 per week</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-chesapeake-gateways-ambassador-triangle-virginia/7904651465</t>
+  </si>
+  <si>
+    <t>Communications and Outreach Specialist</t>
+  </si>
+  <si>
+    <t>Conservation Corps MN/IA</t>
+  </si>
+  <si>
+    <t>St. Paul, MN</t>
+  </si>
+  <si>
+    <t>$2,600 per month</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-communications-and-outreach-specialist-st-paul-minnesota/5160629542</t>
+  </si>
+  <si>
+    <t>Conservation Program Coordinator</t>
+  </si>
+  <si>
+    <t>Rocky Mountain Youth Corps</t>
+  </si>
+  <si>
+    <t>Taos, NM</t>
+  </si>
+  <si>
+    <t>$47,840 - $54,080 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-program-coordinator-taos-new-mexico/6370754095</t>
+  </si>
+  <si>
+    <t>Data Management Specialist - Alaska Marine Mammal Observer Program</t>
+  </si>
+  <si>
+    <t>Pacific States Marine Fisheries Commission</t>
+  </si>
+  <si>
+    <t>Juneau, AK</t>
+  </si>
+  <si>
+    <t>$27.43 - $43.62 per hour</t>
+  </si>
+  <si>
+    <t>fisheries-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-data-management-specialist---alaska-marine-mammal-observer-program-juneau-alaska/9587760934</t>
+  </si>
+  <si>
+    <t>Development Coordinator</t>
+  </si>
+  <si>
+    <t>Delaware Highlands Conservancy</t>
+  </si>
+  <si>
+    <t>Beach Lake, PA</t>
+  </si>
+  <si>
+    <t>Salary is dependent upon experience.</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-development-coordinator-beach-lake-pennsylvania/5530145505</t>
+  </si>
+  <si>
+    <t>Environmental Educator - Seasonal</t>
+  </si>
+  <si>
+    <t>Snohomish Conservation District</t>
+  </si>
+  <si>
+    <t>Lake Stevens, WA</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$25.74 - $29.01 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-educator---seasonal-lake-stevens-washington/6705853075</t>
+  </si>
+  <si>
+    <t>Environmental Management Staffer - Healthy Landscapes Goal Team</t>
+  </si>
+  <si>
+    <t>Chesapeake Research Consortium</t>
+  </si>
+  <si>
+    <t>Annapolis, MD</t>
+  </si>
+  <si>
+    <t>$52,432 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-hydrology-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-management-staffer---healthy-landscapes-goal-team-annapolis-maryland/7056567535</t>
+  </si>
+  <si>
+    <t>Farm Bill Wildlife Biologist I, II, or III</t>
+  </si>
+  <si>
+    <t>Pheasants Forever, Inc., and Quail Forever</t>
+  </si>
+  <si>
+    <t>Scobey, MT</t>
+  </si>
+  <si>
+    <t>$45,000 - $53,000 per year</t>
+  </si>
+  <si>
+    <t>ecology-general-stewardship-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-farm-bill-wildlife-biologist-i-ii-or-iii-scobey-montana/5056837464</t>
+  </si>
+  <si>
+    <t>Forestry Aide (Bio Field Tech)</t>
+  </si>
+  <si>
+    <t>California State Parks, Ocotillo Wells District</t>
+  </si>
+  <si>
+    <t>Borrego Springs, CA</t>
+  </si>
+  <si>
+    <t>$21.60 - $26.71 per hour</t>
+  </si>
+  <si>
+    <t>forestry-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forestry-aide-bio-field-tech-borrego-springs-california/6591124571</t>
+  </si>
+  <si>
+    <t>Forestry and Field Specialist</t>
+  </si>
+  <si>
+    <t>Various, MN</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forestry-and-field-specialist-various-minnesota/9888659017</t>
+  </si>
+  <si>
+    <t>Information Officer – Land Acquisition Specialist</t>
+  </si>
+  <si>
+    <t>NEIWPCC</t>
+  </si>
+  <si>
+    <t>Albany, NY</t>
+  </si>
+  <si>
+    <t>$65,000 - $80,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-information-officer--land-acquisition-specialist-albany-new-york/8279443628</t>
+  </si>
+  <si>
+    <t>Lac Tele Community Reserve Program Manager</t>
+  </si>
+  <si>
+    <t>Wild Conservation Society</t>
+  </si>
+  <si>
+    <t>Epena, Africa</t>
+  </si>
+  <si>
+    <t>Competitive Salary commensurate with Experience</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-lac-tele-community-reserve-program-manager-epena-africa/7866149605</t>
+  </si>
+  <si>
+    <t>M.S. Assistantship: Evaluating Professional Readiness in the Forestry Sector</t>
+  </si>
+  <si>
+    <t>Mississippi State University</t>
+  </si>
+  <si>
+    <t>Starkville, MS</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>$20,000 per year</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-ms-assistantship-evaluating-professional-readiness-in-the-forestry-sector-starkville-mississippi/3451092394</t>
+  </si>
+  <si>
+    <t>Mapping and Data Specialist</t>
+  </si>
+  <si>
+    <t>admin-leadership-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-mapping-and-data-specialist-various-minnesota/7121368039</t>
+  </si>
+  <si>
+    <t>Operations and Planning Specialist</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-operations-and-planning-specialist-st-paul-minnesota/5473756858</t>
+  </si>
+  <si>
+    <t>Operations Manager</t>
+  </si>
+  <si>
+    <t>NatureBridge</t>
+  </si>
+  <si>
+    <t>El Portal, CA</t>
+  </si>
+  <si>
+    <t>$52,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-operations-manager-el-portal-california/1357171720</t>
+  </si>
+  <si>
+    <t>Paid AmeriCorps Volunteer</t>
+  </si>
+  <si>
+    <t>AmeriCorps READY</t>
+  </si>
+  <si>
+    <t>Detroit, MI</t>
+  </si>
+  <si>
+    <t>$12 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-paid-americorps-volunteer-detroit-michigan/4362178397</t>
+  </si>
+  <si>
+    <t>Philanthropy Director</t>
+  </si>
+  <si>
+    <t>Wilderness Workshop</t>
+  </si>
+  <si>
+    <t>Carbondale, CO</t>
+  </si>
+  <si>
+    <t>$107,000 - $148,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-philanthropy-director-carbondale-colorado/9391284187</t>
+  </si>
+  <si>
+    <t>Seasonal Prescribed Fire Crewmember</t>
+  </si>
+  <si>
+    <t>Georgia Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Pembroke, GA</t>
+  </si>
+  <si>
+    <t>$14 - $17 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-seasonal-prescribed-fire-crewmember-pembroke-georgia/3415244982</t>
+  </si>
+  <si>
+    <t>Steamtown Chesapeake Gateways Ambassador</t>
+  </si>
+  <si>
+    <t>Scranton, PA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-steamtown-chesapeake-gateways-ambassador-scranton-pennsylvania/6302422948</t>
+  </si>
+  <si>
+    <t>Urban and Community Forestry Placement</t>
+  </si>
+  <si>
+    <t>$2,500 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-urban-and-community-forestry-placement-various-minnesota/3293863077</t>
+  </si>
+  <si>
+    <t>Visitor Services Information Assistant</t>
+  </si>
+  <si>
+    <t>U.S. Forest Service</t>
+  </si>
+  <si>
+    <t>Hamilton, MT</t>
+  </si>
+  <si>
+    <t>$19.52 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-visitor-services-information-assistant-hamilton-montana/7779908554</t>
+  </si>
+  <si>
+    <t>Water Crew Manager</t>
+  </si>
+  <si>
+    <t>Friends of the Urban Forest</t>
+  </si>
+  <si>
+    <t>$38.07 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-water-crew-manager-san-francisco-california/8662643007</t>
+  </si>
+  <si>
+    <t>Water Resources Engineer</t>
+  </si>
+  <si>
+    <t>Biohabitats, Inc</t>
+  </si>
+  <si>
+    <t>Middletown, CT</t>
+  </si>
+  <si>
+    <t>$95,000 - $110,000 per year</t>
+  </si>
+  <si>
+    <t>hydrology-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-water-resources-engineer-middletown-connecticut/1460889888</t>
+  </si>
+  <si>
+    <t>Watering Technician</t>
+  </si>
+  <si>
+    <t>$28.41 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-watering-technician-san-francisco-california/8667795093</t>
+  </si>
+  <si>
+    <t>Advancement Director</t>
+  </si>
+  <si>
+    <t>United to Learn</t>
+  </si>
+  <si>
+    <t>Dallas, Texas</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d971a850f68b4633b89fdcefd0aefe6f-advancement-director-united-to-learn-dallas</t>
+  </si>
+  <si>
+    <t>Apprentice Teacher for 6-8 Math &amp; Science</t>
+  </si>
+  <si>
+    <t>Wissahickon Charter School</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 47000.00 - 47000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/da0810b300fc466f88a2fe068dc47858-apprentice-teacher-for-6-8-math-science-wissahickon-charter-school-philadelphia</t>
+  </si>
+  <si>
+    <t>Assistant Attorney General</t>
+  </si>
+  <si>
+    <t>Office of the Massachusetts Attorney General</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 90125.00 - 134513.00/year</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/cba4135460af4cf4b9eb8478e5f2efcf-assistant-attorney-general-office-of-the-massachusetts-attorney-general-boston</t>
+  </si>
+  <si>
+    <t>Associate – Employment Lawyer</t>
+  </si>
+  <si>
+    <t>Keenan &amp; Bhatia, LLC</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/de8552ec0bd9463c982bc65bce5388bf-associate-employment-lawyer-keenan-bhatia-llc-new-york</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/b3fb7fa437784a2bb5c290693ce65bb3-associate-employment-lawyer-keenan-bhatia-llc-new-york</t>
+  </si>
+  <si>
+    <t>Bi-lingual Staff Attorney</t>
+  </si>
+  <si>
+    <t>Rutgers Law School - Newark Clinical Program</t>
+  </si>
+  <si>
+    <t>Newark, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c29b4d07f6cc478cb206a07800e88e41-bi-lingual-staff-attorney-rutgers-law-school-newark-clinical-program-newark</t>
+  </si>
+  <si>
+    <t>Bilingual Client Advocate</t>
+  </si>
+  <si>
+    <t>Volunteer Legal Advocates</t>
+  </si>
+  <si>
+    <t>Rockville, Maryland</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cef53bdeebb54b26ad7e23962694f5f7-bilingual-client-advocate-volunteer-legal-advocates-rockville</t>
+  </si>
+  <si>
+    <t>Bilingual Intake Counselor, Prevention</t>
+  </si>
+  <si>
+    <t>St. Vincent de Paul Society of Marin County</t>
+  </si>
+  <si>
+    <t>San Rafael, California</t>
+  </si>
+  <si>
+    <t>USD 32.00/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1a25cfcbd871406f9531039988b54cab-bilingual-intake-counselor-prevention-st-vincent-de-paul-society-of-marin-county-san-rafael</t>
+  </si>
+  <si>
+    <t>Career Specialist II</t>
+  </si>
+  <si>
+    <t>Neighborhood House</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>USD 28.65 - 31.83/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2fad5c6cc9854a75a25ebf81b2f66c2a-career-specialist-ii-neighborhood-house-seattle</t>
+  </si>
+  <si>
+    <t>Chief Marketing Officer</t>
+  </si>
+  <si>
+    <t>The Clean Slate Initiative</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 225000.00 - 260000.00/year</t>
+  </si>
+  <si>
+    <t>Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/44da590051e045ddacddf92173e70bef-chief-marketing-officer-the-clean-slate-initiative-orlando</t>
+  </si>
+  <si>
+    <t>Clinical Counselor -- Community-Based</t>
+  </si>
+  <si>
+    <t>Dorchester Alcohol and Drug Commission</t>
+  </si>
+  <si>
+    <t>Summerville, South Carolina</t>
+  </si>
+  <si>
+    <t>USD 60000.00/year</t>
+  </si>
+  <si>
+    <t>Mental Health, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/eb6ce18157e840e087796ddbfcf80076-clinical-counselor-community-based-dorchester-alcohol-and-drug-commission-summerville</t>
+  </si>
+  <si>
+    <t>Community Engagement Coordinator</t>
+  </si>
+  <si>
+    <t>United Neighborhood Houses</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cca27b8f26b7456ea320dbfd376d2c4a-community-engagement-coordinator-united-neighborhood-houses-new-york</t>
+  </si>
+  <si>
+    <t>Community Roots Charter School, Academic Interventionist, Grades 6-8, 2026-2027</t>
+  </si>
+  <si>
+    <t>Community Roots Charter School</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 65894.00 - 121360.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/afc7caadff3e40208f1ba7f19330ecfc-community-roots-charter-school-academic-interventionist-grades-6-8-2026-2027-community-roots-charter-school-kings-county</t>
+  </si>
+  <si>
+    <t>Consultant</t>
+  </si>
+  <si>
+    <t>MQ Foundation</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 40.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>Health Medicine, Mental Health, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0493487f044b432495426084120f274b-consultant-mq-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Coordinador/a Territorial Programa de Fortalecimiento y Desarrollo de Cadenas Productivas - TARTAGAL</t>
+  </si>
+  <si>
+    <t>Asociación Civil Pata Pila</t>
+  </si>
+  <si>
+    <t>Tartagal, Salta, AR</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/06e8274bd08746299eba68a19297bed9-coordinadora-territorial-programa-de-fortalecimiento-y-desarrollo-de-cadenas-productivas-tartagal-asociacion-civil-pata-pila-tartagal</t>
+  </si>
+  <si>
+    <t>Coordinator of Data and Evaluation</t>
+  </si>
+  <si>
+    <t>RF CUNY (Institute for Justice and Opportunity)</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 62000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Prison Reform</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/50d8387386fc49c9b48622ba42c8d6b6-coordinator-of-data-and-evaluation-rf-cuny-institute-for-justice-and-opportunity-new-york</t>
+  </si>
+  <si>
+    <t>Counseling Manager</t>
+  </si>
+  <si>
+    <t>Ability Now Bay Area</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Education, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/847bcc44cfec44f996562d58ef6acbda-counseling-manager-ability-now-bay-area-oakland</t>
+  </si>
+  <si>
+    <t>Deputy Chief: Investigate Law Enforcement Misconduct (3917)</t>
+  </si>
+  <si>
+    <t>New York State Office of the Attorney General</t>
+  </si>
+  <si>
+    <t>USD 202178.00 - 202178.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/1c9e2dd1ab8a4e969f6d349c3a61074e-deputy-chief-investigate-law-enforcement-misconduct-3917-new-york-state-office-of-the-attorney-general-new-york</t>
+  </si>
+  <si>
+    <t>Deputy Legal Director</t>
+  </si>
+  <si>
+    <t>ACLU of Alaska</t>
+  </si>
+  <si>
+    <t>Anchorage, Alaska</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/e9b4516a979c4e759578394f668c1022-deputy-legal-director-aclu-of-alaska-anchorage</t>
+  </si>
+  <si>
+    <t>Development Associate</t>
+  </si>
+  <si>
+    <t>The Tanzanian Children's Fund</t>
+  </si>
+  <si>
+    <t>Cambridge, Massachusetts</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5d755dae31264966a505595483330ef4-development-associate-the-tanzanian-childrens-fund-cambridge</t>
+  </si>
+  <si>
+    <t>A More Perfect Union: The Jewish Partnership for Democracy</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f39dfbb0125144e28420efed686b2a46-development-associate-a-more-perfect-union-the-jewish-partnership-for-democracy-kings-county</t>
+  </si>
+  <si>
+    <t>Methodist Justice Ministry</t>
+  </si>
+  <si>
+    <t>Fort Worth, Texas</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Crime Safety, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/262de69a050646e9becd31da807468dc-development-coordinator-methodist-justice-ministry-fort-worth</t>
+  </si>
+  <si>
+    <t>Development Director VISTA (Great opportunity for college graduates looking to take a gap year)</t>
+  </si>
+  <si>
+    <t>We Strive for Literacy</t>
+  </si>
+  <si>
+    <t>Vista, California</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 32000.00 - 32000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e3bb7fad40c84263a1335cfcca6e9fdb-development-director-vista-great-opportunity-for-college-graduates-looking-to-take-a-gap-year-we-strive-for-literacy-vista</t>
+  </si>
+  <si>
+    <t>Development Manager</t>
+  </si>
+  <si>
+    <t>Center for US Global Leadership</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>International Relations, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e898380603524ec28ae642dc21627fa8-development-manager-center-for-us-global-leadership-washington</t>
+  </si>
+  <si>
+    <t>Director of Community Partnerships &amp; Creative Aging</t>
+  </si>
+  <si>
+    <t>Goddard House in Brookline Assisted Living</t>
+  </si>
+  <si>
+    <t>Brookline, MA</t>
+  </si>
+  <si>
+    <t>Philanthropy, Seniors Retirement, Veterans</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/761001a1c2354064b2c83fcc4cc88843-director-of-community-partnerships-creative-aging-goddard-house-in-brookline-assisted-living-brookline</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>The 1932 Criterion Theatre</t>
+  </si>
+  <si>
+    <t>Bar Harbor, Maine</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8705b6c0ebb54383ab9e10505b087a0c-director-of-development-the-1932-criterion-theatre-bar-harbor</t>
+  </si>
+  <si>
+    <t>Director, Development Operations and Systems</t>
+  </si>
+  <si>
+    <t>GoodPower</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/90d1f650366a4b7eab4394f2907dda6b-director-development-operations-and-systems-goodpower-boston</t>
+  </si>
+  <si>
+    <t>Director, District Partnerships (K12 Sales)</t>
+  </si>
+  <si>
+    <t>National Math and Science Initiative, Inc.</t>
+  </si>
+  <si>
+    <t>USD 134640.00 - 154836.00/year</t>
+  </si>
+  <si>
+    <t>Education, Children Youth, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a2b0704e3a3548529bbe789d184b35e1-director-district-partnerships-k12-sales-national-math-and-science-initiative-inc-houston</t>
+  </si>
+  <si>
+    <t>Educational Content Editor</t>
+  </si>
+  <si>
+    <t>Partnership to End Addiction</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dc71dfae5a7b48de9f5418d0bf035126-educational-content-editor-partnership-to-end-addiction-new-york</t>
+  </si>
+  <si>
+    <t>Elder Law Unit Staff Attorney</t>
+  </si>
+  <si>
+    <t>South Coastal Counties Legal Services Inc.</t>
+  </si>
+  <si>
+    <t>Hyannis, MA</t>
+  </si>
+  <si>
+    <t>USD 79177.50 - 121095.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Legal Assistance, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2d9e9018be394e01acfa2373850ee95e-elder-law-unit-staff-attorney-south-coastal-counties-legal-services-inc-hyannis</t>
+  </si>
+  <si>
+    <t>Employment Specialist, Workforce Transition &amp; Reemployment</t>
+  </si>
+  <si>
+    <t>The Welcoming Center</t>
+  </si>
+  <si>
+    <t>USD 52500.00 - 64000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Economic Development, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1070416a09e741629c17d9b88438e87e-employment-specialist-workforce-transition-reemployment-the-welcoming-center-philadelphia</t>
+  </si>
+  <si>
+    <t>Executive Assistant</t>
+  </si>
+  <si>
+    <t>ACLU of Georgia</t>
+  </si>
+  <si>
+    <t>Atlanta, Georgia</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c5c2c975d41f4707870747b9b52c9ea6-executive-assistant-aclu-of-georgia-atlanta</t>
+  </si>
+  <si>
     <t>Executive Director</t>
   </si>
   <si>
@@ -49,16 +1036,754 @@
     <t>Issaquah, Washington</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>USD 150000.00 - 165000.00/year</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/consultant-job/839e032df6f649fda9b94311e26db636-executive-director-clover-search-works-issaquah</t>
+  </si>
+  <si>
+    <t>Student Action with Farmworkers (SAF)</t>
+  </si>
+  <si>
+    <t>Durham, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/512b5891ccb24cff95591cb037bbe66b-executive-director-student-action-with-farmworkers-saf-durham</t>
+  </si>
+  <si>
+    <t>Bikemore</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Transportation, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/de3fd081d62b49d09dc925d7aa5e7fa1-executive-director-bikemore-baltimore</t>
+  </si>
+  <si>
+    <t>Finance and Operations Manager</t>
+  </si>
+  <si>
+    <t>Groundwork USA</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/653bba34935e4bcba6bfd8318f5262e1-finance-and-operations-manager-groundwork-usa-yonkers</t>
+  </si>
+  <si>
+    <t>Finance Assistant</t>
+  </si>
+  <si>
+    <t>Mass Farmers Markets</t>
+  </si>
+  <si>
+    <t>Westborough, MA</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 19.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Agriculture, Hunger Food Security, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1504e484c64a4d67835f507e080ccaa8-finance-assistant-mass-farmers-markets-westborough</t>
+  </si>
+  <si>
+    <t>Fund Development Associate</t>
+  </si>
+  <si>
+    <t>Elizabeth Coalition to House the Homeless</t>
+  </si>
+  <si>
+    <t>Elizabeth, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4c1d9f51ea2a43f793497c926b3ae9d4-fund-development-associate-elizabeth-coalition-to-house-the-homeless-elizabeth</t>
+  </si>
+  <si>
+    <t>HR and Operations Manager</t>
+  </si>
+  <si>
+    <t>Emma's Torch</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Hunger Food Security, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/15f0b744b0de47a2984708d1333c1b22-hr-and-operations-manager-emmas-torch-kings-county</t>
+  </si>
+  <si>
+    <t>Silver Spring, Maryland</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/eecc21620cfb467e85b5bf0e93f89cee-hr-and-operations-manager-emmas-torch-silver-spring</t>
+  </si>
+  <si>
+    <t>Job Developer</t>
+  </si>
+  <si>
+    <t>USD 67000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Job Workplace, Prison Reform</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fa8aea4485a54231923ec900bd98cc44-job-developer-rf-cuny-institute-for-justice-and-opportunity-new-york</t>
+  </si>
+  <si>
+    <t>League Operations Lead/Coordinator</t>
+  </si>
+  <si>
+    <t>San Francisco Youth Soccer</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 25.01/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1d61db9920f7476e8f6bf4243ac06a1a-league-operations-leadcoordinator-san-francisco-youth-soccer-san-francisco</t>
+  </si>
+  <si>
+    <t>Legislative Director</t>
+  </si>
+  <si>
+    <t>Office of Assemblymember David Siffert</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Immigrants Or Refugees, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/fb51bb17a92d43b5be33bfc4d3f76304-legislative-director-office-of-assemblymember-david-siffert-new-york</t>
+  </si>
+  <si>
+    <t>Licensed Counselor for Adolescent &amp; Adult Outpatient Services</t>
+  </si>
+  <si>
+    <t>USD 48500.00/year</t>
+  </si>
+  <si>
+    <t>Mental Health, Substance Abuse Addiction, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/2ac74d9f385a4bf6b3e61fcefd907602-licensed-counselor-for-adolescent-adult-outpatient-services-dorchester-alcohol-and-drug-commission-summerville</t>
+  </si>
+  <si>
+    <t>Litigation Program Fellowship, Fall 2027-2029</t>
+  </si>
+  <si>
+    <t>Animal Legal Defense Fund</t>
+  </si>
+  <si>
+    <t>USD 71509.00 - 71509.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Environment, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7f92587254a146d3b34219948c10acfa-litigation-program-fellowship-fall-2027-2029-animal-legal-defense-fund-cotati</t>
+  </si>
+  <si>
+    <t>Lower School Science Teacher (Temporary)</t>
+  </si>
+  <si>
+    <t>Abraham Joshua Heschel School</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/546eaeee3cdd48c4aa7cb277472f4476-lower-school-science-teacher-temporary-abraham-joshua-heschel-school-new-york</t>
+  </si>
+  <si>
+    <t>Manager of Coaching Operations, Workforce Transition Initiative</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 67000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0c575d282afa41429791e1f828ce0ae4-manager-of-coaching-operations-workforce-transition-initiative-the-welcoming-center-philadelphia</t>
+  </si>
+  <si>
+    <t>Middle School History Teacher for 7th &amp; 8th Grade</t>
+  </si>
+  <si>
+    <t>Liberty LEADS in New York City</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 40.00 - 50.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/781e23b424ea4dd0b5522ffa2e671432-middle-school-history-teacher-for-7th-8th-grade-liberty-leads-in-new-york-city-new-york</t>
+  </si>
+  <si>
+    <t>Officer, Foundation Relations</t>
+  </si>
+  <si>
+    <t>Hispanic Access Foundation</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/73c8637708434c509cf0675540d03271-officer-foundation-relations-hispanic-access-foundation-washington</t>
+  </si>
+  <si>
+    <t>Operations &amp; Finance Associate</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5ae4f753118346029325315926fffc38-operations-finance-associate-emmas-torch-silver-spring</t>
+  </si>
+  <si>
+    <t>Operations Associate</t>
+  </si>
+  <si>
+    <t>Vote Kansas PAC</t>
+  </si>
+  <si>
+    <t>Kansas City, Kansas</t>
+  </si>
+  <si>
+    <t>USD 5500.00 - 5500.00/month</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/69c25245b0264320a3d120ed477531e7-operations-associate-vote-kansas-pac-kansas-city</t>
+  </si>
+  <si>
+    <t>OPPORTUNITY: ELEMENTARY CLASSROOM TEACHER: 2nd, 3rd or 4th-5th GRADE (NATIVE LEVEL OF ENGLISH PROFICIENCY REQUIRED)</t>
+  </si>
+  <si>
+    <t>Colegio Americano del Sur</t>
+  </si>
+  <si>
+    <t>Santa Lucia, Escuintla, GT</t>
+  </si>
+  <si>
+    <t>USD 18000.00 - 20000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/af39077bf5284c31a606c2c6b2192a9a-opportunity-elementary-classroom-teacher-2nd-3rd-or-4th-5th-grade-native-level-of-english-proficiency-required-colegio-americano-del-sur-santa-lucia</t>
+  </si>
+  <si>
+    <t>OPPORTUNITY: HIGH LEVEL ENGLISH PROFICIENT, CERTIFIED High School English Language Arts Classroom (Teacher/Fellow) (Including school related activity involvement)</t>
+  </si>
+  <si>
+    <t>Santa Lucia, Cotzumaguapa, ES, GT</t>
+  </si>
+  <si>
+    <t>USD 1800.00 - 2000.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Conflict Resolution, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d39005ab21b94cbf9d5bd5bf132454d2-opportunity-high-level-english-proficient-certified-high-school-english-language-arts-classroom-teacherfellow-including-school-related-activity-involvement-colegio-americano-del-sur-santa-lucia-cotzumaguapa</t>
+  </si>
+  <si>
+    <t>OPPORTUNITY: Middle School Social Studies/English Classroom Teacher (High Level of English Proficiency Speaker required.)</t>
+  </si>
+  <si>
+    <t>Santa Lucia, Cotzumaguapa, ESCUINTLA, GT</t>
+  </si>
+  <si>
+    <t>Science Technology, Rural Areas, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a8ecf61a40034b379b422c047ba36f0c-opportunity-middle-school-social-studiesenglish-classroom-teacher-high-level-of-english-proficiency-speaker-required-colegio-americano-del-sur-santa-lucia-cotzumaguapa</t>
+  </si>
+  <si>
+    <t>Organizing Manager</t>
+  </si>
+  <si>
+    <t>Citizen Action/Illinois</t>
+  </si>
+  <si>
+    <t>Chicago, IL</t>
+  </si>
+  <si>
+    <t>USD 65000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/64f3be73acaa4a76837c2af1b52cc9db-organizing-manager-citizen-actionillinois-chicago</t>
+  </si>
+  <si>
+    <t>Paid Political Canvasser</t>
+  </si>
+  <si>
+    <t>Battleground New York</t>
+  </si>
+  <si>
+    <t>Spring Valley, New York</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 28.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/0cbb83bb26f44fe4aefb60ec3a21a61b-paid-political-canvasser-battleground-new-york-spring-valley</t>
+  </si>
+  <si>
+    <t>Paralegal</t>
+  </si>
+  <si>
+    <t>The Public Interest Law Center</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Housing Homelessness, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0d950cc4ab9d4b02b950a55043cc2546-paralegal-the-public-interest-law-center-philadelphia</t>
+  </si>
+  <si>
+    <t>Partnerships &amp; Ecosystem Manager</t>
+  </si>
+  <si>
+    <t>Accelerate Resilience L.A. (ARLA)</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5c52abce5b6e4327a63a30d98a67e24d-partnerships-ecosystem-manager-accelerate-resilience-la-arla-los-angeles</t>
+  </si>
+  <si>
+    <t>Person Centered Planning Specialist</t>
+  </si>
+  <si>
+    <t>WeAchieve Inc</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/de1dda3e8ae0426698134c19f8941762-person-centered-planning-specialist-weachieve-inc-silver-spring</t>
+  </si>
+  <si>
+    <t>Policy &amp; Outreach Manager</t>
+  </si>
+  <si>
+    <t>National Taxpayers Union</t>
+  </si>
+  <si>
+    <t>Policy, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/35494e08a03e44859617c35ee7bcf4de-policy-outreach-manager-national-taxpayers-union-washington</t>
+  </si>
+  <si>
+    <t>Principal Associate, Field Operations</t>
+  </si>
+  <si>
+    <t>Pew Charitable Trusts</t>
+  </si>
+  <si>
+    <t>USD 109800.00 - 122700.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/38bda1dbb2d7437bb46e178ceed1c6ce-principal-associate-field-operations-pew-charitable-trusts-washington</t>
+  </si>
+  <si>
+    <t>Pro Bono Manager (JD Required)</t>
+  </si>
+  <si>
+    <t>Children's Law Center</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 98000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2938e6efdcc241b0b328f3bc6e926bab-pro-bono-manager-jd-required-childrens-law-center-washington</t>
+  </si>
+  <si>
+    <t>PROGRAM COORDINATOR</t>
+  </si>
+  <si>
+    <t>Oak Ridge Environmental Peace Alliance (OREPA)</t>
+  </si>
+  <si>
+    <t>Knoxville, Tennessee</t>
+  </si>
+  <si>
+    <t>Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/527953eaeec248d1a10ff4db74636a50-program-coordinator-oak-ridge-environmental-peace-alliance-orepa-knoxville</t>
+  </si>
+  <si>
+    <t>Program Director</t>
+  </si>
+  <si>
+    <t>Wilmette Theatre</t>
+  </si>
+  <si>
+    <t>Wilmette, Illinois</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 66000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cce29d97df0f409ebc3bdd09f8eb3cfa-program-director-wilmette-theatre-wilmette</t>
+  </si>
+  <si>
+    <t>Program Director, Cornerstone Patterson</t>
+  </si>
+  <si>
+    <t>East Side House Settlement</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>USD 51000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0a2f42b32c7a444ba21037ac23407ca5-program-director-cornerstone-patterson-east-side-house-settlement-bronx-county</t>
+  </si>
+  <si>
+    <t>Project Attorney: 18-Month Term, Adult Survivors Act (3914)</t>
+  </si>
+  <si>
+    <t>Hauppauge, New York</t>
+  </si>
+  <si>
+    <t>USD 91506.00 - 190644.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/47d68570e14747b2971159ba87651c2e-project-attorney-18-month-term-adult-survivors-act-3914-new-york-state-office-of-the-attorney-general-hauppauge</t>
+  </si>
+  <si>
+    <t>Project Attorney: 18-Month Term, Adult Survivors Act (3915)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/0d9966dfe8844243a8b162a8f31ba067-project-attorney-18-month-term-adult-survivors-act-3915-new-york-state-office-of-the-attorney-general-new-york</t>
+  </si>
+  <si>
+    <t>Project Attorney: 18-Month Term, Adult Survivors Act (3916)</t>
+  </si>
+  <si>
+    <t>White Plains, New York</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/919718da9b7c4442a5fd01b58df78a37-project-attorney-18-month-term-adult-survivors-act-3916-new-york-state-office-of-the-attorney-general-white-plains</t>
+  </si>
+  <si>
+    <t>Protection Officer</t>
+  </si>
+  <si>
+    <t>Protection International AISBL</t>
+  </si>
+  <si>
+    <t>Saint-Gilles, Bruxelles, BE</t>
+  </si>
+  <si>
+    <t>EUR 3500.00 - 4000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/638038ff53a346c4958267ef4cc6f429-protection-officer-protection-international-aisbl-saint-gilles</t>
+  </si>
+  <si>
+    <t>Rapid Response Workforce Transition Project Manager</t>
+  </si>
+  <si>
+    <t>USD 63000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ce5e448f93fc41709b8e2c0cad529847-rapid-response-workforce-transition-project-manager-the-welcoming-center-philadelphia</t>
+  </si>
+  <si>
+    <t>Senior Accountant</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ff2410e286d14a03950604dfb17597f5-senior-accountant-new-york</t>
+  </si>
+  <si>
+    <t>Senior Counsel for Environmental Justice</t>
+  </si>
+  <si>
+    <t>Southern Coalition for Social Justice</t>
+  </si>
+  <si>
+    <t>USD 100000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Environment, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0f09d7298a2849eb8970ee5871132576-senior-counsel-for-environmental-justice-southern-coalition-for-social-justice-durham</t>
+  </si>
+  <si>
+    <t>Senior Director of Communications</t>
+  </si>
+  <si>
+    <t>Latinos Progresando</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c342ec28bc3946e986c32f9e42a6b5db-senior-director-of-communications-latinos-progresando-chicago</t>
+  </si>
+  <si>
+    <t>SENIOR LEGAL ADVOCATE, IMMIGRATION</t>
+  </si>
+  <si>
+    <t>Survivor Justice Center</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>USD 34.00 - 38.00/hour</t>
+  </si>
+  <si>
+    <t>Family, Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/961f26260cee4c069dc92de1fb735d6d-senior-legal-advocate-immigration-survivor-justice-center-los-angeles</t>
+  </si>
+  <si>
+    <t>Senior Manager of Finance, Grants &amp; Operations</t>
+  </si>
+  <si>
+    <t>Communities United for Restorative Justice (CURYJ)</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/299e32602ad44fcc9cfdb0677f907ad6-senior-manager-of-finance-grants-operations-communities-united-for-restorative-justice-curyj-oakland</t>
+  </si>
+  <si>
+    <t>Shared Program Manager - Environmental Education and Community Engagement</t>
+  </si>
+  <si>
+    <t>Painted Bins, a project of Sustainable Marin</t>
+  </si>
+  <si>
+    <t>Remote (Corte Madera, California)</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d2b960f7f77c40cabbedbc02ca22c18b-shared-program-manager-environmental-education-and-community-engagement-painted-bins-a-project-of-sustainable-marin-corte-madera</t>
+  </si>
+  <si>
+    <t>Social Listening Specialist - Consultancy Opportunity</t>
+  </si>
+  <si>
+    <t>Kamara</t>
+  </si>
+  <si>
+    <t>USD 5000.00 - 6500.00/month</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/a8da9b3a3b454555be0dc9696e6ffbda-social-listening-specialist-consultancy-opportunity-kamara-london</t>
+  </si>
+  <si>
+    <t>Social Worker, Bronx</t>
+  </si>
+  <si>
+    <t>The Children's Law Center NY</t>
+  </si>
+  <si>
+    <t>USD 76500.00 - 105636.28/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/829a40a1dc9c42a7af73b23a39300eb9-social-worker-bronx-the-childrens-law-center-ny-bronx-county</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>Texas RioGrande Legal Aid, Inc. (TRLA)</t>
+  </si>
+  <si>
+    <t>Harlingen, Texas</t>
+  </si>
+  <si>
+    <t>USD 66929.00 - 91067.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/94e8a68f735a4f7288b46d74b45695e3-staff-attorney-texas-riogrande-legal-aid-inc-trla-harlingen</t>
+  </si>
+  <si>
+    <t>Alpine, Texas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6682b6e2faab4b298a70361b8f23a7eb-staff-attorney-texas-riogrande-legal-aid-inc-trla-alpine</t>
+  </si>
+  <si>
+    <t>Victoria, Texas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3a7fa41b5ac545818bb694755fdae940-staff-attorney-texas-riogrande-legal-aid-inc-trla-victoria</t>
+  </si>
+  <si>
+    <t>USD 66000.00 - 98000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0388b7f2c31240ce8f2eb5b195192df7-staff-attorney-methodist-justice-ministry-fort-worth</t>
+  </si>
+  <si>
+    <t>Supervising Attorney - Removal Defense Team</t>
+  </si>
+  <si>
+    <t>The Door's Legal Services Center</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/40fc8bf2b03c4f7090297af791c2e1a5-supervising-attorney-removal-defense-team-the-doors-legal-services-center-new-york</t>
+  </si>
+  <si>
+    <t>Supervising Attorney, Domestic Violence Program</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 88000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Legal Assistance, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f3d084035011422aa9d5f583a670df71-supervising-attorney-domestic-violence-program-volunteer-legal-advocates-rockville</t>
+  </si>
+  <si>
+    <t>Systems Administrator</t>
+  </si>
+  <si>
+    <t>Massachusetts Science &amp; Engineering Fair</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ce29f18e8ae443bb84db0353357791af-systems-administrator-massachusetts-science-engineering-fair-cambridge</t>
+  </si>
+  <si>
+    <t>Temporary Staff Attorney, NYC</t>
+  </si>
+  <si>
+    <t>Safe Passage Project Corporation</t>
+  </si>
+  <si>
+    <t>USD 85614.91 - 99806.29/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e6147be800d7451090fae998972eade6-temporary-staff-attorney-nyc-safe-passage-project-corporation-new-york</t>
+  </si>
+  <si>
+    <t>Vice President of Media Engagement</t>
+  </si>
+  <si>
+    <t>Groundwork Collaborative</t>
+  </si>
+  <si>
+    <t>USD 180000.00 - 200000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/2f764ee167104f08a2932268880e3a8c-vice-president-of-media-engagement-groundwork-collaborative-washington</t>
+  </si>
+  <si>
+    <t>Volunteer and Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Mission Nutrition Deforest</t>
+  </si>
+  <si>
+    <t>DeForest, Wisconsin</t>
+  </si>
+  <si>
+    <t>USD 21.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c17d1b366c244afe9b70ba3f3a4fc99f-volunteer-and-operations-coordinator-mission-nutrition-deforest-deforest</t>
   </si>
 </sst>
 </file>
@@ -444,7 +2169,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -483,8 +2208,730 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F13" t="s">
+        <v>80</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>85</v>
+      </c>
+      <c r="F14" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" t="s">
+        <v>96</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>98</v>
+      </c>
+      <c r="B17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>101</v>
+      </c>
+      <c r="F17" t="s">
+        <v>102</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>107</v>
+      </c>
+      <c r="F18" t="s">
+        <v>50</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E19" t="s">
+        <v>113</v>
+      </c>
+      <c r="F19" t="s">
+        <v>114</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" t="s">
+        <v>49</v>
+      </c>
+      <c r="F20" t="s">
+        <v>117</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" t="s">
+        <v>49</v>
+      </c>
+      <c r="F21" t="s">
+        <v>120</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" t="s">
+        <v>124</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>125</v>
+      </c>
+      <c r="F22" t="s">
+        <v>50</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>127</v>
+      </c>
+      <c r="B23" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" t="s">
+        <v>129</v>
+      </c>
+      <c r="D23" t="s">
+        <v>42</v>
+      </c>
+      <c r="E23" t="s">
+        <v>130</v>
+      </c>
+      <c r="F23" t="s">
+        <v>131</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>133</v>
+      </c>
+      <c r="B24" t="s">
+        <v>134</v>
+      </c>
+      <c r="C24" t="s">
+        <v>135</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>136</v>
+      </c>
+      <c r="F24" t="s">
+        <v>50</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>138</v>
+      </c>
+      <c r="B25" t="s">
+        <v>139</v>
+      </c>
+      <c r="C25" t="s">
+        <v>140</v>
+      </c>
+      <c r="D25" t="s">
+        <v>72</v>
+      </c>
+      <c r="E25" t="s">
+        <v>141</v>
+      </c>
+      <c r="F25" t="s">
+        <v>114</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>143</v>
+      </c>
+      <c r="B26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" t="s">
+        <v>144</v>
+      </c>
+      <c r="D26" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" t="s">
+        <v>117</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>146</v>
+      </c>
+      <c r="B27" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" t="s">
+        <v>95</v>
+      </c>
+      <c r="D27" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" t="s">
+        <v>147</v>
+      </c>
+      <c r="F27" t="s">
+        <v>114</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>149</v>
+      </c>
+      <c r="B28" t="s">
+        <v>150</v>
+      </c>
+      <c r="C28" t="s">
+        <v>151</v>
+      </c>
+      <c r="D28" t="s">
+        <v>72</v>
+      </c>
+      <c r="E28" t="s">
+        <v>152</v>
+      </c>
+      <c r="F28" t="s">
+        <v>44</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>154</v>
+      </c>
+      <c r="B29" t="s">
+        <v>155</v>
+      </c>
+      <c r="C29" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>156</v>
+      </c>
+      <c r="F29" t="s">
+        <v>157</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>159</v>
+      </c>
+      <c r="B30" t="s">
+        <v>160</v>
+      </c>
+      <c r="C30" t="s">
+        <v>161</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>162</v>
+      </c>
+      <c r="F30" t="s">
+        <v>163</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>165</v>
+      </c>
+      <c r="B31" t="s">
+        <v>155</v>
+      </c>
+      <c r="C31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>166</v>
+      </c>
+      <c r="F31" t="s">
+        <v>114</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -540,7 +2987,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -581,31 +3028,2119 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>168</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>169</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>170</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>171</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>172</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>173</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>14</v>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E4" t="s">
+        <v>184</v>
+      </c>
+      <c r="F4" t="s">
+        <v>185</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C5" t="s">
+        <v>189</v>
+      </c>
+      <c r="D5" t="s">
+        <v>171</v>
+      </c>
+      <c r="E5" t="s">
+        <v>190</v>
+      </c>
+      <c r="F5" t="s">
+        <v>191</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D6" t="s">
+        <v>171</v>
+      </c>
+      <c r="E6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F6" t="s">
+        <v>191</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>194</v>
+      </c>
+      <c r="B7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D7" t="s">
+        <v>171</v>
+      </c>
+      <c r="E7" t="s">
+        <v>197</v>
+      </c>
+      <c r="F7" t="s">
+        <v>185</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>199</v>
+      </c>
+      <c r="B8" t="s">
+        <v>200</v>
+      </c>
+      <c r="C8" t="s">
+        <v>201</v>
+      </c>
+      <c r="D8" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F8" t="s">
+        <v>203</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>205</v>
+      </c>
+      <c r="B9" t="s">
+        <v>206</v>
+      </c>
+      <c r="C9" t="s">
+        <v>207</v>
+      </c>
+      <c r="D9" t="s">
+        <v>171</v>
+      </c>
+      <c r="E9" t="s">
+        <v>208</v>
+      </c>
+      <c r="F9" t="s">
+        <v>209</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>211</v>
+      </c>
+      <c r="B10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C10" t="s">
+        <v>213</v>
+      </c>
+      <c r="D10" t="s">
+        <v>171</v>
+      </c>
+      <c r="E10" t="s">
+        <v>214</v>
+      </c>
+      <c r="F10" t="s">
+        <v>215</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>217</v>
+      </c>
+      <c r="B11" t="s">
+        <v>218</v>
+      </c>
+      <c r="C11" t="s">
+        <v>219</v>
+      </c>
+      <c r="D11" t="s">
+        <v>171</v>
+      </c>
+      <c r="E11" t="s">
+        <v>220</v>
+      </c>
+      <c r="F11" t="s">
+        <v>221</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>223</v>
+      </c>
+      <c r="B12" t="s">
+        <v>224</v>
+      </c>
+      <c r="C12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D12" t="s">
+        <v>171</v>
+      </c>
+      <c r="E12" t="s">
+        <v>226</v>
+      </c>
+      <c r="F12" t="s">
+        <v>227</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>229</v>
+      </c>
+      <c r="B13" t="s">
+        <v>230</v>
+      </c>
+      <c r="C13" t="s">
+        <v>189</v>
+      </c>
+      <c r="D13" t="s">
+        <v>171</v>
+      </c>
+      <c r="E13" t="s">
+        <v>185</v>
+      </c>
+      <c r="F13" t="s">
+        <v>231</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>233</v>
+      </c>
+      <c r="B14" t="s">
+        <v>234</v>
+      </c>
+      <c r="C14" t="s">
+        <v>235</v>
+      </c>
+      <c r="D14" t="s">
+        <v>171</v>
+      </c>
+      <c r="E14" t="s">
+        <v>236</v>
+      </c>
+      <c r="F14" t="s">
+        <v>237</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>239</v>
+      </c>
+      <c r="B15" t="s">
+        <v>240</v>
+      </c>
+      <c r="C15" t="s">
+        <v>219</v>
+      </c>
+      <c r="D15" t="s">
+        <v>241</v>
+      </c>
+      <c r="E15" t="s">
+        <v>242</v>
+      </c>
+      <c r="F15" t="s">
+        <v>243</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>245</v>
+      </c>
+      <c r="B16" t="s">
+        <v>246</v>
+      </c>
+      <c r="C16" t="s">
+        <v>247</v>
+      </c>
+      <c r="D16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E16" t="s">
+        <v>185</v>
+      </c>
+      <c r="F16" t="s">
+        <v>185</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>249</v>
+      </c>
+      <c r="B17" t="s">
+        <v>250</v>
+      </c>
+      <c r="C17" t="s">
+        <v>189</v>
+      </c>
+      <c r="D17" t="s">
+        <v>171</v>
+      </c>
+      <c r="E17" t="s">
+        <v>251</v>
+      </c>
+      <c r="F17" t="s">
+        <v>252</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>254</v>
+      </c>
+      <c r="B18" t="s">
+        <v>255</v>
+      </c>
+      <c r="C18" t="s">
+        <v>256</v>
+      </c>
+      <c r="D18" t="s">
+        <v>171</v>
+      </c>
+      <c r="E18" t="s">
+        <v>257</v>
+      </c>
+      <c r="F18" t="s">
+        <v>258</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>260</v>
+      </c>
+      <c r="B19" t="s">
+        <v>261</v>
+      </c>
+      <c r="C19" t="s">
+        <v>189</v>
+      </c>
+      <c r="D19" t="s">
+        <v>171</v>
+      </c>
+      <c r="E19" t="s">
+        <v>262</v>
+      </c>
+      <c r="F19" t="s">
+        <v>185</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>264</v>
+      </c>
+      <c r="B20" t="s">
+        <v>265</v>
+      </c>
+      <c r="C20" t="s">
+        <v>266</v>
+      </c>
+      <c r="D20" t="s">
+        <v>171</v>
+      </c>
+      <c r="E20" t="s">
+        <v>267</v>
+      </c>
+      <c r="F20" t="s">
+        <v>268</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>270</v>
+      </c>
+      <c r="B21" t="s">
+        <v>271</v>
+      </c>
+      <c r="C21" t="s">
+        <v>272</v>
+      </c>
+      <c r="D21" t="s">
+        <v>171</v>
+      </c>
+      <c r="E21" t="s">
+        <v>185</v>
+      </c>
+      <c r="F21" t="s">
+        <v>273</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>270</v>
+      </c>
+      <c r="B22" t="s">
+        <v>275</v>
+      </c>
+      <c r="C22" t="s">
+        <v>219</v>
+      </c>
+      <c r="D22" t="s">
+        <v>171</v>
+      </c>
+      <c r="E22" t="s">
+        <v>276</v>
+      </c>
+      <c r="F22" t="s">
+        <v>277</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" t="s">
+        <v>279</v>
+      </c>
+      <c r="C23" t="s">
+        <v>280</v>
+      </c>
+      <c r="D23" t="s">
+        <v>171</v>
+      </c>
+      <c r="E23" t="s">
+        <v>281</v>
+      </c>
+      <c r="F23" t="s">
+        <v>282</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>284</v>
+      </c>
+      <c r="B24" t="s">
+        <v>285</v>
+      </c>
+      <c r="C24" t="s">
+        <v>286</v>
+      </c>
+      <c r="D24" t="s">
+        <v>287</v>
+      </c>
+      <c r="E24" t="s">
+        <v>288</v>
+      </c>
+      <c r="F24" t="s">
+        <v>179</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>290</v>
+      </c>
+      <c r="B25" t="s">
+        <v>291</v>
+      </c>
+      <c r="C25" t="s">
+        <v>292</v>
+      </c>
+      <c r="D25" t="s">
+        <v>171</v>
+      </c>
+      <c r="E25" t="s">
+        <v>293</v>
+      </c>
+      <c r="F25" t="s">
+        <v>294</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>296</v>
+      </c>
+      <c r="B26" t="s">
+        <v>297</v>
+      </c>
+      <c r="C26" t="s">
+        <v>298</v>
+      </c>
+      <c r="D26" t="s">
+        <v>171</v>
+      </c>
+      <c r="E26" t="s">
+        <v>267</v>
+      </c>
+      <c r="F26" t="s">
+        <v>299</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>301</v>
+      </c>
+      <c r="B27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C27" t="s">
+        <v>303</v>
+      </c>
+      <c r="D27" t="s">
+        <v>171</v>
+      </c>
+      <c r="E27" t="s">
+        <v>257</v>
+      </c>
+      <c r="F27" t="s">
+        <v>304</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>306</v>
+      </c>
+      <c r="B28" t="s">
+        <v>307</v>
+      </c>
+      <c r="C28" t="s">
+        <v>219</v>
+      </c>
+      <c r="D28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E28" t="s">
+        <v>308</v>
+      </c>
+      <c r="F28" t="s">
+        <v>309</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>311</v>
+      </c>
+      <c r="B29" t="s">
+        <v>312</v>
+      </c>
+      <c r="C29" t="s">
+        <v>219</v>
+      </c>
+      <c r="D29" t="s">
+        <v>171</v>
+      </c>
+      <c r="E29" t="s">
+        <v>313</v>
+      </c>
+      <c r="F29" t="s">
+        <v>314</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>316</v>
+      </c>
+      <c r="B30" t="s">
+        <v>317</v>
+      </c>
+      <c r="C30" t="s">
+        <v>189</v>
+      </c>
+      <c r="D30" t="s">
+        <v>171</v>
+      </c>
+      <c r="E30" t="s">
+        <v>276</v>
+      </c>
+      <c r="F30" t="s">
+        <v>318</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>320</v>
+      </c>
+      <c r="B31" t="s">
+        <v>321</v>
+      </c>
+      <c r="C31" t="s">
+        <v>322</v>
+      </c>
+      <c r="D31" t="s">
+        <v>171</v>
+      </c>
+      <c r="E31" t="s">
+        <v>323</v>
+      </c>
+      <c r="F31" t="s">
+        <v>324</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>326</v>
+      </c>
+      <c r="B32" t="s">
+        <v>327</v>
+      </c>
+      <c r="C32" t="s">
+        <v>177</v>
+      </c>
+      <c r="D32" t="s">
+        <v>171</v>
+      </c>
+      <c r="E32" t="s">
+        <v>328</v>
+      </c>
+      <c r="F32" t="s">
+        <v>329</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>331</v>
+      </c>
+      <c r="B33" t="s">
+        <v>332</v>
+      </c>
+      <c r="C33" t="s">
+        <v>333</v>
+      </c>
+      <c r="D33" t="s">
+        <v>171</v>
+      </c>
+      <c r="E33" t="s">
+        <v>334</v>
+      </c>
+      <c r="F33" t="s">
+        <v>335</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>337</v>
+      </c>
+      <c r="B34" t="s">
+        <v>338</v>
+      </c>
+      <c r="C34" t="s">
+        <v>339</v>
+      </c>
+      <c r="D34" t="s">
+        <v>171</v>
+      </c>
+      <c r="E34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F34" t="s">
+        <v>185</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>337</v>
+      </c>
+      <c r="B35" t="s">
+        <v>342</v>
+      </c>
+      <c r="C35" t="s">
+        <v>343</v>
+      </c>
+      <c r="D35" t="s">
+        <v>171</v>
+      </c>
+      <c r="E35" t="s">
+        <v>344</v>
+      </c>
+      <c r="F35" t="s">
+        <v>345</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>337</v>
+      </c>
+      <c r="B36" t="s">
+        <v>347</v>
+      </c>
+      <c r="C36" t="s">
+        <v>348</v>
+      </c>
+      <c r="D36" t="s">
+        <v>171</v>
+      </c>
+      <c r="E36" t="s">
+        <v>349</v>
+      </c>
+      <c r="F36" t="s">
+        <v>350</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>352</v>
+      </c>
+      <c r="B37" t="s">
+        <v>353</v>
+      </c>
+      <c r="C37" t="s">
+        <v>219</v>
+      </c>
+      <c r="D37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E37" t="s">
+        <v>276</v>
+      </c>
+      <c r="F37" t="s">
+        <v>354</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>356</v>
+      </c>
+      <c r="B38" t="s">
+        <v>357</v>
+      </c>
+      <c r="C38" t="s">
+        <v>358</v>
+      </c>
+      <c r="D38" t="s">
+        <v>359</v>
+      </c>
+      <c r="E38" t="s">
+        <v>360</v>
+      </c>
+      <c r="F38" t="s">
+        <v>361</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>363</v>
+      </c>
+      <c r="B39" t="s">
+        <v>364</v>
+      </c>
+      <c r="C39" t="s">
+        <v>365</v>
+      </c>
+      <c r="D39" t="s">
+        <v>171</v>
+      </c>
+      <c r="E39" t="s">
+        <v>366</v>
+      </c>
+      <c r="F39" t="s">
+        <v>209</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>368</v>
+      </c>
+      <c r="B40" t="s">
+        <v>369</v>
+      </c>
+      <c r="C40" t="s">
+        <v>235</v>
+      </c>
+      <c r="D40" t="s">
+        <v>171</v>
+      </c>
+      <c r="E40" t="s">
+        <v>370</v>
+      </c>
+      <c r="F40" t="s">
+        <v>371</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>368</v>
+      </c>
+      <c r="B41" t="s">
+        <v>369</v>
+      </c>
+      <c r="C41" t="s">
+        <v>373</v>
+      </c>
+      <c r="D41" t="s">
+        <v>171</v>
+      </c>
+      <c r="E41" t="s">
+        <v>370</v>
+      </c>
+      <c r="F41" t="s">
+        <v>371</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>375</v>
+      </c>
+      <c r="B42" t="s">
+        <v>250</v>
+      </c>
+      <c r="C42" t="s">
+        <v>189</v>
+      </c>
+      <c r="D42" t="s">
+        <v>171</v>
+      </c>
+      <c r="E42" t="s">
+        <v>376</v>
+      </c>
+      <c r="F42" t="s">
+        <v>377</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>379</v>
+      </c>
+      <c r="B43" t="s">
+        <v>380</v>
+      </c>
+      <c r="C43" t="s">
+        <v>381</v>
+      </c>
+      <c r="D43" t="s">
+        <v>171</v>
+      </c>
+      <c r="E43" t="s">
+        <v>382</v>
+      </c>
+      <c r="F43" t="s">
+        <v>383</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>385</v>
+      </c>
+      <c r="B44" t="s">
+        <v>386</v>
+      </c>
+      <c r="C44" t="s">
+        <v>189</v>
+      </c>
+      <c r="D44" t="s">
+        <v>171</v>
+      </c>
+      <c r="E44" t="s">
+        <v>293</v>
+      </c>
+      <c r="F44" t="s">
+        <v>387</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>389</v>
+      </c>
+      <c r="B45" t="s">
+        <v>224</v>
+      </c>
+      <c r="C45" t="s">
+        <v>225</v>
+      </c>
+      <c r="D45" t="s">
+        <v>171</v>
+      </c>
+      <c r="E45" t="s">
+        <v>390</v>
+      </c>
+      <c r="F45" t="s">
+        <v>391</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>393</v>
+      </c>
+      <c r="B46" t="s">
+        <v>394</v>
+      </c>
+      <c r="C46" t="s">
+        <v>219</v>
+      </c>
+      <c r="D46" t="s">
+        <v>171</v>
+      </c>
+      <c r="E46" t="s">
+        <v>395</v>
+      </c>
+      <c r="F46" t="s">
+        <v>396</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>398</v>
+      </c>
+      <c r="B47" t="s">
+        <v>399</v>
+      </c>
+      <c r="C47" t="s">
+        <v>189</v>
+      </c>
+      <c r="D47" t="s">
+        <v>241</v>
+      </c>
+      <c r="E47" t="s">
+        <v>400</v>
+      </c>
+      <c r="F47" t="s">
+        <v>237</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>402</v>
+      </c>
+      <c r="B48" t="s">
+        <v>327</v>
+      </c>
+      <c r="C48" t="s">
+        <v>177</v>
+      </c>
+      <c r="D48" t="s">
+        <v>171</v>
+      </c>
+      <c r="E48" t="s">
+        <v>403</v>
+      </c>
+      <c r="F48" t="s">
+        <v>329</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>405</v>
+      </c>
+      <c r="B49" t="s">
+        <v>406</v>
+      </c>
+      <c r="C49" t="s">
+        <v>407</v>
+      </c>
+      <c r="D49" t="s">
+        <v>408</v>
+      </c>
+      <c r="E49" t="s">
+        <v>409</v>
+      </c>
+      <c r="F49" t="s">
+        <v>215</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>411</v>
+      </c>
+      <c r="B50" t="s">
+        <v>412</v>
+      </c>
+      <c r="C50" t="s">
+        <v>219</v>
+      </c>
+      <c r="D50" t="s">
+        <v>171</v>
+      </c>
+      <c r="E50" t="s">
+        <v>413</v>
+      </c>
+      <c r="F50" t="s">
+        <v>414</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>416</v>
+      </c>
+      <c r="B51" t="s">
+        <v>369</v>
+      </c>
+      <c r="C51" t="s">
+        <v>373</v>
+      </c>
+      <c r="D51" t="s">
+        <v>171</v>
+      </c>
+      <c r="E51" t="s">
+        <v>366</v>
+      </c>
+      <c r="F51" t="s">
+        <v>371</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>418</v>
+      </c>
+      <c r="B52" t="s">
+        <v>419</v>
+      </c>
+      <c r="C52" t="s">
+        <v>420</v>
+      </c>
+      <c r="D52" t="s">
+        <v>287</v>
+      </c>
+      <c r="E52" t="s">
+        <v>421</v>
+      </c>
+      <c r="F52" t="s">
+        <v>185</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>423</v>
+      </c>
+      <c r="B53" t="s">
+        <v>424</v>
+      </c>
+      <c r="C53" t="s">
+        <v>425</v>
+      </c>
+      <c r="D53" t="s">
+        <v>171</v>
+      </c>
+      <c r="E53" t="s">
+        <v>426</v>
+      </c>
+      <c r="F53" t="s">
+        <v>185</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>428</v>
+      </c>
+      <c r="B54" t="s">
+        <v>424</v>
+      </c>
+      <c r="C54" t="s">
+        <v>429</v>
+      </c>
+      <c r="D54" t="s">
+        <v>171</v>
+      </c>
+      <c r="E54" t="s">
+        <v>430</v>
+      </c>
+      <c r="F54" t="s">
+        <v>431</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>433</v>
+      </c>
+      <c r="B55" t="s">
+        <v>424</v>
+      </c>
+      <c r="C55" t="s">
+        <v>434</v>
+      </c>
+      <c r="D55" t="s">
+        <v>171</v>
+      </c>
+      <c r="E55" t="s">
+        <v>426</v>
+      </c>
+      <c r="F55" t="s">
+        <v>435</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>437</v>
+      </c>
+      <c r="B56" t="s">
+        <v>438</v>
+      </c>
+      <c r="C56" t="s">
+        <v>439</v>
+      </c>
+      <c r="D56" t="s">
+        <v>171</v>
+      </c>
+      <c r="E56" t="s">
+        <v>440</v>
+      </c>
+      <c r="F56" t="s">
+        <v>441</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>443</v>
+      </c>
+      <c r="B57" t="s">
+        <v>444</v>
+      </c>
+      <c r="C57" t="s">
+        <v>445</v>
+      </c>
+      <c r="D57" t="s">
+        <v>408</v>
+      </c>
+      <c r="E57" t="s">
+        <v>446</v>
+      </c>
+      <c r="F57" t="s">
+        <v>185</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>448</v>
+      </c>
+      <c r="B58" t="s">
+        <v>449</v>
+      </c>
+      <c r="C58" t="s">
+        <v>177</v>
+      </c>
+      <c r="D58" t="s">
+        <v>171</v>
+      </c>
+      <c r="E58" t="s">
+        <v>450</v>
+      </c>
+      <c r="F58" t="s">
+        <v>451</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>453</v>
+      </c>
+      <c r="B59" t="s">
+        <v>454</v>
+      </c>
+      <c r="C59" t="s">
+        <v>455</v>
+      </c>
+      <c r="D59" t="s">
+        <v>171</v>
+      </c>
+      <c r="E59" t="s">
+        <v>456</v>
+      </c>
+      <c r="F59" t="s">
+        <v>457</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>459</v>
+      </c>
+      <c r="B60" t="s">
+        <v>460</v>
+      </c>
+      <c r="C60" t="s">
+        <v>373</v>
+      </c>
+      <c r="D60" t="s">
+        <v>171</v>
+      </c>
+      <c r="E60" t="s">
+        <v>461</v>
+      </c>
+      <c r="F60" t="s">
+        <v>462</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>464</v>
+      </c>
+      <c r="B61" t="s">
+        <v>465</v>
+      </c>
+      <c r="C61" t="s">
+        <v>292</v>
+      </c>
+      <c r="D61" t="s">
+        <v>171</v>
+      </c>
+      <c r="E61" t="s">
+        <v>334</v>
+      </c>
+      <c r="F61" t="s">
+        <v>466</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>468</v>
+      </c>
+      <c r="B62" t="s">
+        <v>469</v>
+      </c>
+      <c r="C62" t="s">
+        <v>292</v>
+      </c>
+      <c r="D62" t="s">
+        <v>171</v>
+      </c>
+      <c r="E62" t="s">
+        <v>470</v>
+      </c>
+      <c r="F62" t="s">
+        <v>185</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>472</v>
+      </c>
+      <c r="B63" t="s">
+        <v>473</v>
+      </c>
+      <c r="C63" t="s">
+        <v>292</v>
+      </c>
+      <c r="D63" t="s">
+        <v>171</v>
+      </c>
+      <c r="E63" t="s">
+        <v>474</v>
+      </c>
+      <c r="F63" t="s">
+        <v>215</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>476</v>
+      </c>
+      <c r="B64" t="s">
+        <v>477</v>
+      </c>
+      <c r="C64" t="s">
+        <v>478</v>
+      </c>
+      <c r="D64" t="s">
+        <v>171</v>
+      </c>
+      <c r="E64" t="s">
+        <v>226</v>
+      </c>
+      <c r="F64" t="s">
+        <v>479</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>481</v>
+      </c>
+      <c r="B65" t="s">
+        <v>482</v>
+      </c>
+      <c r="C65" t="s">
+        <v>483</v>
+      </c>
+      <c r="D65" t="s">
+        <v>171</v>
+      </c>
+      <c r="E65" t="s">
+        <v>484</v>
+      </c>
+      <c r="F65" t="s">
+        <v>485</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>487</v>
+      </c>
+      <c r="B66" t="s">
+        <v>488</v>
+      </c>
+      <c r="C66" t="s">
+        <v>489</v>
+      </c>
+      <c r="D66" t="s">
+        <v>171</v>
+      </c>
+      <c r="E66" t="s">
+        <v>490</v>
+      </c>
+      <c r="F66" t="s">
+        <v>491</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>493</v>
+      </c>
+      <c r="B67" t="s">
+        <v>261</v>
+      </c>
+      <c r="C67" t="s">
+        <v>494</v>
+      </c>
+      <c r="D67" t="s">
+        <v>171</v>
+      </c>
+      <c r="E67" t="s">
+        <v>495</v>
+      </c>
+      <c r="F67" t="s">
+        <v>185</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>497</v>
+      </c>
+      <c r="B68" t="s">
+        <v>261</v>
+      </c>
+      <c r="C68" t="s">
+        <v>189</v>
+      </c>
+      <c r="D68" t="s">
+        <v>171</v>
+      </c>
+      <c r="E68" t="s">
+        <v>495</v>
+      </c>
+      <c r="F68" t="s">
+        <v>185</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>499</v>
+      </c>
+      <c r="B69" t="s">
+        <v>261</v>
+      </c>
+      <c r="C69" t="s">
+        <v>500</v>
+      </c>
+      <c r="D69" t="s">
+        <v>171</v>
+      </c>
+      <c r="E69" t="s">
+        <v>495</v>
+      </c>
+      <c r="F69" t="s">
+        <v>185</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>502</v>
+      </c>
+      <c r="B70" t="s">
+        <v>503</v>
+      </c>
+      <c r="C70" t="s">
+        <v>504</v>
+      </c>
+      <c r="D70" t="s">
+        <v>287</v>
+      </c>
+      <c r="E70" t="s">
+        <v>505</v>
+      </c>
+      <c r="F70" t="s">
+        <v>506</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>508</v>
+      </c>
+      <c r="B71" t="s">
+        <v>327</v>
+      </c>
+      <c r="C71" t="s">
+        <v>177</v>
+      </c>
+      <c r="D71" t="s">
+        <v>171</v>
+      </c>
+      <c r="E71" t="s">
+        <v>509</v>
+      </c>
+      <c r="F71" t="s">
+        <v>329</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>511</v>
+      </c>
+      <c r="B72" t="s">
+        <v>185</v>
+      </c>
+      <c r="C72" t="s">
+        <v>189</v>
+      </c>
+      <c r="D72" t="s">
+        <v>171</v>
+      </c>
+      <c r="E72" t="s">
+        <v>197</v>
+      </c>
+      <c r="F72" t="s">
+        <v>512</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>514</v>
+      </c>
+      <c r="B73" t="s">
+        <v>515</v>
+      </c>
+      <c r="C73" t="s">
+        <v>343</v>
+      </c>
+      <c r="D73" t="s">
+        <v>171</v>
+      </c>
+      <c r="E73" t="s">
+        <v>516</v>
+      </c>
+      <c r="F73" t="s">
+        <v>517</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>519</v>
+      </c>
+      <c r="B74" t="s">
+        <v>520</v>
+      </c>
+      <c r="C74" t="s">
+        <v>521</v>
+      </c>
+      <c r="D74" t="s">
+        <v>171</v>
+      </c>
+      <c r="E74" t="s">
+        <v>344</v>
+      </c>
+      <c r="F74" t="s">
+        <v>185</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>523</v>
+      </c>
+      <c r="B75" t="s">
+        <v>524</v>
+      </c>
+      <c r="C75" t="s">
+        <v>525</v>
+      </c>
+      <c r="D75" t="s">
+        <v>171</v>
+      </c>
+      <c r="E75" t="s">
+        <v>526</v>
+      </c>
+      <c r="F75" t="s">
+        <v>527</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>529</v>
+      </c>
+      <c r="B76" t="s">
+        <v>530</v>
+      </c>
+      <c r="C76" t="s">
+        <v>256</v>
+      </c>
+      <c r="D76" t="s">
+        <v>171</v>
+      </c>
+      <c r="E76" t="s">
+        <v>531</v>
+      </c>
+      <c r="F76" t="s">
+        <v>532</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>534</v>
+      </c>
+      <c r="B77" t="s">
+        <v>535</v>
+      </c>
+      <c r="C77" t="s">
+        <v>536</v>
+      </c>
+      <c r="D77" t="s">
+        <v>171</v>
+      </c>
+      <c r="E77" t="s">
+        <v>537</v>
+      </c>
+      <c r="F77" t="s">
+        <v>538</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>540</v>
+      </c>
+      <c r="B78" t="s">
+        <v>541</v>
+      </c>
+      <c r="C78" t="s">
+        <v>219</v>
+      </c>
+      <c r="D78" t="s">
+        <v>241</v>
+      </c>
+      <c r="E78" t="s">
+        <v>542</v>
+      </c>
+      <c r="F78" t="s">
+        <v>543</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>545</v>
+      </c>
+      <c r="B79" t="s">
+        <v>546</v>
+      </c>
+      <c r="C79" t="s">
+        <v>489</v>
+      </c>
+      <c r="D79" t="s">
+        <v>171</v>
+      </c>
+      <c r="E79" t="s">
+        <v>547</v>
+      </c>
+      <c r="F79" t="s">
+        <v>191</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>549</v>
+      </c>
+      <c r="B80" t="s">
+        <v>550</v>
+      </c>
+      <c r="C80" t="s">
+        <v>551</v>
+      </c>
+      <c r="D80" t="s">
+        <v>171</v>
+      </c>
+      <c r="E80" t="s">
+        <v>552</v>
+      </c>
+      <c r="F80" t="s">
+        <v>553</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>549</v>
+      </c>
+      <c r="B81" t="s">
+        <v>550</v>
+      </c>
+      <c r="C81" t="s">
+        <v>555</v>
+      </c>
+      <c r="D81" t="s">
+        <v>171</v>
+      </c>
+      <c r="E81" t="s">
+        <v>552</v>
+      </c>
+      <c r="F81" t="s">
+        <v>553</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>549</v>
+      </c>
+      <c r="B82" t="s">
+        <v>550</v>
+      </c>
+      <c r="C82" t="s">
+        <v>557</v>
+      </c>
+      <c r="D82" t="s">
+        <v>171</v>
+      </c>
+      <c r="E82" t="s">
+        <v>552</v>
+      </c>
+      <c r="F82" t="s">
+        <v>553</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>549</v>
+      </c>
+      <c r="B83" t="s">
+        <v>279</v>
+      </c>
+      <c r="C83" t="s">
+        <v>280</v>
+      </c>
+      <c r="D83" t="s">
+        <v>171</v>
+      </c>
+      <c r="E83" t="s">
+        <v>559</v>
+      </c>
+      <c r="F83" t="s">
+        <v>282</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>561</v>
+      </c>
+      <c r="B84" t="s">
+        <v>562</v>
+      </c>
+      <c r="C84" t="s">
+        <v>189</v>
+      </c>
+      <c r="D84" t="s">
+        <v>171</v>
+      </c>
+      <c r="E84" t="s">
+        <v>563</v>
+      </c>
+      <c r="F84" t="s">
+        <v>203</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>565</v>
+      </c>
+      <c r="B85" t="s">
+        <v>200</v>
+      </c>
+      <c r="C85" t="s">
+        <v>201</v>
+      </c>
+      <c r="D85" t="s">
+        <v>171</v>
+      </c>
+      <c r="E85" t="s">
+        <v>566</v>
+      </c>
+      <c r="F85" t="s">
+        <v>567</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>569</v>
+      </c>
+      <c r="B86" t="s">
+        <v>570</v>
+      </c>
+      <c r="C86" t="s">
+        <v>272</v>
+      </c>
+      <c r="D86" t="s">
+        <v>171</v>
+      </c>
+      <c r="E86" t="s">
+        <v>571</v>
+      </c>
+      <c r="F86" t="s">
+        <v>572</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>574</v>
+      </c>
+      <c r="B87" t="s">
+        <v>575</v>
+      </c>
+      <c r="C87" t="s">
+        <v>189</v>
+      </c>
+      <c r="D87" t="s">
+        <v>241</v>
+      </c>
+      <c r="E87" t="s">
+        <v>576</v>
+      </c>
+      <c r="F87" t="s">
+        <v>577</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>579</v>
+      </c>
+      <c r="B88" t="s">
+        <v>580</v>
+      </c>
+      <c r="C88" t="s">
+        <v>292</v>
+      </c>
+      <c r="D88" t="s">
+        <v>171</v>
+      </c>
+      <c r="E88" t="s">
+        <v>581</v>
+      </c>
+      <c r="F88" t="s">
+        <v>582</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>584</v>
+      </c>
+      <c r="B89" t="s">
+        <v>585</v>
+      </c>
+      <c r="C89" t="s">
+        <v>586</v>
+      </c>
+      <c r="D89" t="s">
+        <v>359</v>
+      </c>
+      <c r="E89" t="s">
+        <v>587</v>
+      </c>
+      <c r="F89" t="s">
+        <v>588</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>589</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-09-29.xlsx
+++ b/docs/xlsx/jobs-2026-09-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="965">
   <si>
     <t>Title</t>
   </si>
@@ -520,6 +520,24 @@
     <t>https://www.conservationjobboard.com/job-listing-watering-technician-san-francisco-california/8667795093</t>
   </si>
   <si>
+    <t>Administrative Assistant 2</t>
+  </si>
+  <si>
+    <t>Augusta University</t>
+  </si>
+  <si>
+    <t>Augusta, Georgia</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/2fa3e5f0f71b469fa1519fb1b10d27b3-administrative-assistant-2-augusta-university-augusta</t>
+  </si>
+  <si>
     <t>Advancement Director</t>
   </si>
   <si>
@@ -529,9 +547,6 @@
     <t>Dallas, Texas</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>USD 80000.00 - 110000.00/year</t>
   </si>
   <si>
@@ -541,6 +556,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/d971a850f68b4633b89fdcefd0aefe6f-advancement-director-united-to-learn-dallas</t>
   </si>
   <si>
+    <t>American Economic Security Index Senior Director</t>
+  </si>
+  <si>
+    <t>Goodnation</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 155000.00 - 170000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dd8f9fe3e9024b41aceb88a345facb92-american-economic-security-index-senior-director-goodnation-new-york</t>
+  </si>
+  <si>
     <t>Apprentice Teacher for 6-8 Math &amp; Science</t>
   </si>
   <si>
@@ -571,9 +604,6 @@
     <t>USD 90125.00 - 134513.00/year</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/government-job/cba4135460af4cf4b9eb8478e5f2efcf-assistant-attorney-general-office-of-the-massachusetts-attorney-general-boston</t>
   </si>
   <si>
@@ -598,6 +628,42 @@
     <t>https://www.idealist.org/en/business-job/b3fb7fa437784a2bb5c290693ce65bb3-associate-employment-lawyer-keenan-bhatia-llc-new-york</t>
   </si>
   <si>
+    <t>Associate Director of Government Affairs</t>
+  </si>
+  <si>
+    <t>American Civil Liberties Union of New Jersey</t>
+  </si>
+  <si>
+    <t>Remote (New Jersey)</t>
+  </si>
+  <si>
+    <t>USD 110000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/94bc056abdf243338d445678ceff6062-associate-director-of-government-affairs-american-civil-liberties-union-of-new-jersey-newark</t>
+  </si>
+  <si>
+    <t>Behavioral Youth Counselor</t>
+  </si>
+  <si>
+    <t>Youth Villages</t>
+  </si>
+  <si>
+    <t>Memphis, Tennessee</t>
+  </si>
+  <si>
+    <t>USD 54000.00 - 64000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e9f5d82d795245eaaa0918afb003c9c4-behavioral-youth-counselor-youth-villages-memphis</t>
+  </si>
+  <si>
     <t>Bi-lingual Staff Attorney</t>
   </si>
   <si>
@@ -613,6 +679,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/c29b4d07f6cc478cb206a07800e88e41-bi-lingual-staff-attorney-rutgers-law-school-newark-clinical-program-newark</t>
   </si>
   <si>
+    <t>Bilingual (Spanish/English) Mental Health Clinician</t>
+  </si>
+  <si>
+    <t>Children's Advocacy Center of Suffolk County</t>
+  </si>
+  <si>
+    <t>Boston, MA</t>
+  </si>
+  <si>
+    <t>USD 65000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Victim Support, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/165ff1395f2848a686fae7cc2128b515-bilingual-spanishenglish-mental-health-clinician-childrens-advocacy-center-of-suffolk-county-boston</t>
+  </si>
+  <si>
     <t>Bilingual Client Advocate</t>
   </si>
   <si>
@@ -649,6 +733,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/1a25cfcbd871406f9531039988b54cab-bilingual-intake-counselor-prevention-st-vincent-de-paul-society-of-marin-county-san-rafael</t>
   </si>
   <si>
+    <t>Camas Meditation Hall Executive Director</t>
+  </si>
+  <si>
+    <t>Clover Search Works</t>
+  </si>
+  <si>
+    <t>Port Townsend, Washington</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/5ba2863888cb4a32a6fa98f1c86ab5fc-camas-meditation-hall-executive-director-clover-search-works-port-townsend</t>
+  </si>
+  <si>
     <t>Career Specialist II</t>
   </si>
   <si>
@@ -673,9 +772,6 @@
     <t>The Clean Slate Initiative</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
     <t>USD 225000.00 - 260000.00/year</t>
   </si>
   <si>
@@ -685,6 +781,24 @@
     <t>https://www.idealist.org/en/job/44da590051e045ddacddf92173e70bef-chief-marketing-officer-the-clean-slate-initiative-orlando</t>
   </si>
   <si>
+    <t>Client Service Coordinator</t>
+  </si>
+  <si>
+    <t>Ecumenical Ministries of Oregon</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>USD 31.19/hour</t>
+  </si>
+  <si>
+    <t>Disability, Housing Homelessness, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e6414edad5be42bca2917e68481b6b07-client-service-coordinator-ecumenical-ministries-of-oregon-portland</t>
+  </si>
+  <si>
     <t>Clinical Counselor -- Community-Based</t>
   </si>
   <si>
@@ -703,6 +817,24 @@
     <t>https://www.idealist.org/en/government-job/eb6ce18157e840e087796ddbfcf80076-clinical-counselor-community-based-dorchester-alcohol-and-drug-commission-summerville</t>
   </si>
   <si>
+    <t>Clinical Director, OMH Outpatient Clinic</t>
+  </si>
+  <si>
+    <t>Bridging Access To Care Inc</t>
+  </si>
+  <si>
+    <t>Brooklyn, New York 11249</t>
+  </si>
+  <si>
+    <t>USD 105000.00/year</t>
+  </si>
+  <si>
+    <t>Mental Health, Substance Abuse Addiction, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7e6b02c5ee454249bdcda1e7277ba47b-clinical-director-omh-outpatient-clinic-bridging-access-to-care-inc-brooklyn</t>
+  </si>
+  <si>
     <t>Community Engagement Coordinator</t>
   </si>
   <si>
@@ -751,6 +883,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/0493487f044b432495426084120f274b-consultant-mq-foundation-new-york</t>
   </si>
   <si>
+    <t>Cook (Interim Housing Shelter)</t>
+  </si>
+  <si>
+    <t>Sarah's Circle (Chicago)</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 19.00 - 22.50/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Lgbtq, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9c7c01207fb14b8d982d76fa87c2305b-cook-interim-housing-shelter-sarahs-circle-chicago-chicago</t>
+  </si>
+  <si>
     <t>Coordinador/a Territorial Programa de Fortalecimiento y Desarrollo de Cadenas Productivas - TARTAGAL</t>
   </si>
   <si>
@@ -904,6 +1054,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/e898380603524ec28ae642dc21627fa8-development-manager-center-for-us-global-leadership-washington</t>
   </si>
   <si>
+    <t>Louisiana Bucket Brigade</t>
+  </si>
+  <si>
+    <t>New Orleans, Louisiana</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/02ae2e11460b400d818181ad277c4953-development-manager-louisiana-bucket-brigade-new-orleans</t>
+  </si>
+  <si>
     <t>Director of Community Partnerships &amp; Creative Aging</t>
   </si>
   <si>
@@ -934,6 +1099,90 @@
     <t>https://www.idealist.org/en/nonprofit-job/8705b6c0ebb54383ab9e10505b087a0c-director-of-development-the-1932-criterion-theatre-bar-harbor</t>
   </si>
   <si>
+    <t>VOCAL-US</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/47b84cf82f65491b9d68ee97e657816f-director-of-development-vocal-us-kings-county</t>
+  </si>
+  <si>
+    <t>REVERB</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 145000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Environment, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ca2a86c2c32f4587a2bedd5311568033-director-of-development-reverb-portland</t>
+  </si>
+  <si>
+    <t>Director of Finance</t>
+  </si>
+  <si>
+    <t>APANO Communities United Fund</t>
+  </si>
+  <si>
+    <t>USD 99659.00 - 113551.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bbb2e8ba97b243408cac182ec23c0897-director-of-finance-apano-communities-united-fund-portland</t>
+  </si>
+  <si>
+    <t>Director of Legal Services</t>
+  </si>
+  <si>
+    <t>Levitt &amp; Quinn Family Law Center, Inc.</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 150000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f2d58e5fb1ec41f5870cf17ee21e5e5e-director-of-legal-services-levitt-quinn-family-law-center-inc-los-angeles</t>
+  </si>
+  <si>
+    <t>Director of Stewardship and Asset Management</t>
+  </si>
+  <si>
+    <t>Bay Area Community Land Trust</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5acc64ec48ee4cec89b54e7bccc644f6-director-of-stewardship-and-asset-management-bay-area-community-land-trust-berkeley</t>
+  </si>
+  <si>
+    <t>Director, Data &amp; Integration Services</t>
+  </si>
+  <si>
+    <t>Environmental Defense Fund</t>
+  </si>
+  <si>
+    <t>USD 152000.00 - 162000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Climate Change, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/25e0a55c30fb49c2a0529eb2b794db5e-director-data-integration-services-environmental-defense-fund-new-york</t>
+  </si>
+  <si>
     <t>Director, Development Operations and Systems</t>
   </si>
   <si>
@@ -964,6 +1213,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/a2b0704e3a3548529bbe789d184b35e1-director-district-partnerships-k12-sales-national-math-and-science-initiative-inc-houston</t>
   </si>
   <si>
+    <t>Dog Program Coordinator</t>
+  </si>
+  <si>
+    <t>Animal Aid, Inc.</t>
+  </si>
+  <si>
+    <t>USD 21.00/hour</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4f69f7490c324389b932ed145b38ebd6-dog-program-coordinator-animal-aid-inc-portland</t>
+  </si>
+  <si>
     <t>Educational Content Editor</t>
   </si>
   <si>
@@ -976,6 +1240,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/dc71dfae5a7b48de9f5418d0bf035126-educational-content-editor-partnership-to-end-addiction-new-york</t>
   </si>
   <si>
+    <t>Educator [South King County]</t>
+  </si>
+  <si>
+    <t>Geeking Out Kids of Color (GOKiC)</t>
+  </si>
+  <si>
+    <t>White Center, Washington</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 29.25/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/62310d5e6be04241bc873d2813376360-educator-south-king-county-geeking-out-kids-of-color-gokic-white-center</t>
+  </si>
+  <si>
     <t>Elder Law Unit Staff Attorney</t>
   </si>
   <si>
@@ -1030,9 +1312,6 @@
     <t>Executive Director</t>
   </si>
   <si>
-    <t>Clover Search Works</t>
-  </si>
-  <si>
     <t>Issaquah, Washington</t>
   </si>
   <si>
@@ -1072,6 +1351,66 @@
     <t>https://www.idealist.org/en/nonprofit-job/de3fd081d62b49d09dc925d7aa5e7fa1-executive-director-bikemore-baltimore</t>
   </si>
   <si>
+    <t>Association for Death Education and Counseling</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Family, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f29840746b284e68b969dd5e0ef17eb9-executive-director-association-for-death-education-and-counseling-new-york</t>
+  </si>
+  <si>
+    <t>Care Net Pregnancy Center of Indian River County</t>
+  </si>
+  <si>
+    <t>Vero Beach, Florida</t>
+  </si>
+  <si>
+    <t>Family, Men, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8ffb83f8659b4ba48feb5492af707a86-executive-director-care-net-pregnancy-center-of-indian-river-county-vero-beach</t>
+  </si>
+  <si>
+    <t>Executive Director - Wasat Community</t>
+  </si>
+  <si>
+    <t>Wasat Community</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5e2397c6a775424e8892115420e1c317-executive-director-wasat-community-wasat-community-seattle</t>
+  </si>
+  <si>
+    <t>Farmers Market Attendant</t>
+  </si>
+  <si>
+    <t>The People's Market</t>
+  </si>
+  <si>
+    <t>Hyattsville, Maryland</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Agriculture, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/10b6933d179744b0b116f09d4e4b6ee0-farmers-market-attendant-the-peoples-market-hyattsville</t>
+  </si>
+  <si>
     <t>Finance and Operations Manager</t>
   </si>
   <si>
@@ -1093,9 +1432,6 @@
     <t>Westborough, MA</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 19.00 - 20.00/hour</t>
   </si>
   <si>
@@ -1120,6 +1456,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/4c1d9f51ea2a43f793497c926b3ae9d4-fund-development-associate-elizabeth-coalition-to-house-the-homeless-elizabeth</t>
   </si>
   <si>
+    <t>Green Jobs &amp; Landscaping Organizer</t>
+  </si>
+  <si>
+    <t>We Are Comunidad</t>
+  </si>
+  <si>
+    <t>Federal Way, Washington</t>
+  </si>
+  <si>
+    <t>USD 62400.00 - 72800.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/66d541209dec4533a9e1951b6ee6105a-green-jobs-landscaping-organizer-we-are-comunidad-federal-way</t>
+  </si>
+  <si>
     <t>HR and Operations Manager</t>
   </si>
   <si>
@@ -1141,6 +1495,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/eecc21620cfb467e85b5bf0e93f89cee-hr-and-operations-manager-emmas-torch-silver-spring</t>
   </si>
   <si>
+    <t>Industry Relations Coordinator</t>
+  </si>
+  <si>
+    <t>U.S. Grains &amp; BioProducts Council</t>
+  </si>
+  <si>
+    <t>USD 63000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ad7fb65d76fe4e8fb637bcc69f8c3cb4-industry-relations-coordinator-us-grains-bioproducts-council-washington</t>
+  </si>
+  <si>
     <t>Job Developer</t>
   </si>
   <si>
@@ -1249,15 +1618,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/781e23b424ea4dd0b5522ffa2e671432-middle-school-history-teacher-for-7th-8th-grade-liberty-leads-in-new-york-city-new-york</t>
   </si>
   <si>
+    <t>Nontraditional Pathways Success Coordinator</t>
+  </si>
+  <si>
+    <t>St. James School Philadelphia</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8fee07193336432fbe933b3e2fdc3ba9-nontraditional-pathways-success-coordinator-st-james-school-philadelphia-philadelphia</t>
+  </si>
+  <si>
     <t>Officer, Foundation Relations</t>
   </si>
   <si>
     <t>Hispanic Access Foundation</t>
   </si>
   <si>
-    <t>USD 90000.00 - 100000.00/year</t>
-  </si>
-  <si>
     <t>Children Youth, Civic Engagement, Economic Development</t>
   </si>
   <si>
@@ -1336,15 +1717,30 @@
     <t>Chicago, IL</t>
   </si>
   <si>
-    <t>USD 65000.00/year</t>
-  </si>
-  <si>
     <t>Civic Engagement, Education, Environment</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/64f3be73acaa4a76837c2af1b52cc9db-organizing-manager-citizen-actionillinois-chicago</t>
   </si>
   <si>
+    <t>Outreach &amp; Social Services Coordinator</t>
+  </si>
+  <si>
+    <t>Adler Aphasia Center</t>
+  </si>
+  <si>
+    <t>Maywood, NJ</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Health Medicine, Education, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6c13e6a2282846ed8a44b5ea1c3b7057-outreach-social-services-coordinator-adler-aphasia-center-maywood</t>
+  </si>
+  <si>
     <t>Paid Political Canvasser</t>
   </si>
   <si>
@@ -1381,9 +1777,6 @@
     <t>Accelerate Resilience L.A. (ARLA)</t>
   </si>
   <si>
-    <t>Los Angeles, California</t>
-  </si>
-  <si>
     <t>USD 115000.00 - 125000.00/year</t>
   </si>
   <si>
@@ -1408,6 +1801,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/de1dda3e8ae0426698134c19f8941762-person-centered-planning-specialist-weachieve-inc-silver-spring</t>
   </si>
   <si>
+    <t>Philanthropy Officer, Animal Welfare</t>
+  </si>
+  <si>
+    <t>The Humane League</t>
+  </si>
+  <si>
+    <t>USD 95684.00 - 116586.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ff4629b91083402e8d208d5dfe44f217-philanthropy-officer-animal-welfare-the-humane-league-philadelphia</t>
+  </si>
+  <si>
     <t>Policy &amp; Outreach Manager</t>
   </si>
   <si>
@@ -1420,6 +1825,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/35494e08a03e44859617c35ee7bcf4de-policy-outreach-manager-national-taxpayers-union-washington</t>
   </si>
   <si>
+    <t>Policy Fellow</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/14b3f97c3b5a4fb19c7f50ae8bd947cf-policy-fellow-american-civil-liberties-union-of-new-jersey-newark</t>
+  </si>
+  <si>
+    <t>Policy Strategist</t>
+  </si>
+  <si>
+    <t>USD 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/774897a6d08047328f4f6ebc51785334-policy-strategist-american-civil-liberties-union-of-new-jersey-newark</t>
+  </si>
+  <si>
     <t>Principal Associate, Field Operations</t>
   </si>
   <si>
@@ -1444,6 +1864,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/2938e6efdcc241b0b328f3bc6e926bab-pro-bono-manager-jd-required-childrens-law-center-washington</t>
   </si>
   <si>
+    <t>Product Manager</t>
+  </si>
+  <si>
+    <t>Local Public, a Public Benefit Corporation</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/3771b53963934bdbb5bae0df6baabe4b-product-manager-local-public-a-public-benefit-corporation-seattle</t>
+  </si>
+  <si>
+    <t>Program Associate</t>
+  </si>
+  <si>
+    <t>IntermediaryEd</t>
+  </si>
+  <si>
+    <t>USD 74240.00 - 84600.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Philanthropy, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/5cc35ff932e047c5a4caf6c3b05a3df0-program-associate-intermediaryed-newark</t>
+  </si>
+  <si>
     <t>PROGRAM COORDINATOR</t>
   </si>
   <si>
@@ -1522,6 +1969,24 @@
     <t>https://www.idealist.org/en/government-job/919718da9b7c4442a5fd01b58df78a37-project-attorney-18-month-term-adult-survivors-act-3916-new-york-state-office-of-the-attorney-general-white-plains</t>
   </si>
   <si>
+    <t>Project Manager</t>
+  </si>
+  <si>
+    <t>Nuestra Casa de East Palo Alto</t>
+  </si>
+  <si>
+    <t>East Palo Alto, California</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 96000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Environment, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/347a4e63f8f24afa9d7757bb5e836106-project-manager-nuestra-casa-de-east-palo-alto-east-palo-alto</t>
+  </si>
+  <si>
     <t>Protection Officer</t>
   </si>
   <si>
@@ -1540,6 +2005,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/638038ff53a346c4958267ef4cc6f429-protection-officer-protection-international-aisbl-saint-gilles</t>
   </si>
   <si>
+    <t>PUBLIC DEFENDER CLIENT ADVOCATE – LOS ANGELES COUNTY HEAL PROGRAM</t>
+  </si>
+  <si>
+    <t>Partners for Justice</t>
+  </si>
+  <si>
+    <t>USD 52400.00 - 55980.00/year</t>
+  </si>
+  <si>
+    <t>Crime Safety, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bf6c24886a9f4cc6b4a30dee8355081a-public-defender-client-advocate-los-angeles-county-heal-program-partners-for-justice-los-angeles</t>
+  </si>
+  <si>
     <t>Rapid Response Workforce Transition Project Manager</t>
   </si>
   <si>
@@ -1549,6 +2029,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/ce5e448f93fc41709b8e2c0cad529847-rapid-response-workforce-transition-project-manager-the-welcoming-center-philadelphia</t>
   </si>
   <si>
+    <t>S.O.A.R Mentor and Tutor</t>
+  </si>
+  <si>
+    <t>Inspiring Minds NYC</t>
+  </si>
+  <si>
+    <t>Brooklyn, NY</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a327b1bfd74b4ab29ea2bf30c5d55a17-soar-mentor-and-tutor-inspiring-minds-nyc-brooklyn</t>
+  </si>
+  <si>
     <t>Senior Accountant</t>
   </si>
   <si>
@@ -1579,9 +2077,6 @@
     <t>Latinos Progresando</t>
   </si>
   <si>
-    <t>Chicago, Illinois</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/c342ec28bc3946e986c32f9e42a6b5db-senior-director-of-communications-latinos-progresando-chicago</t>
   </si>
   <si>
@@ -1612,9 +2107,6 @@
     <t>USD 115000.00 - 130000.00/year</t>
   </si>
   <si>
-    <t>Children Youth, Community Development, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/299e32602ad44fcc9cfdb0677f907ad6-senior-manager-of-finance-grants-operations-communities-united-for-restorative-justice-curyj-oakland</t>
   </si>
   <si>
@@ -1699,6 +2191,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/0388b7f2c31240ce8f2eb5b195192df7-staff-attorney-methodist-justice-ministry-fort-worth</t>
   </si>
   <si>
+    <t>Staff Attorney 1</t>
+  </si>
+  <si>
+    <t>New York Legal Assistance Group (NYLAG)</t>
+  </si>
+  <si>
+    <t>USD 90262.00 - 100532.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/efca70992ab04645863bcf01c5c39c1f-staff-attorney-1-new-york-legal-assistance-group-nylag-new-york</t>
+  </si>
+  <si>
+    <t>Staff Attorney 2</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7c6155df1efe42e6b67e53d908f68abd-staff-attorney-2-new-york-legal-assistance-group-nylag-new-york</t>
+  </si>
+  <si>
+    <t>Supervising Attorney</t>
+  </si>
+  <si>
+    <t>USD 123277.00 - 147223.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a578d171e9994ca0b8ec905b5d973030-supervising-attorney-new-york-legal-assistance-group-nylag-new-york</t>
+  </si>
+  <si>
     <t>Supervising Attorney - Removal Defense Team</t>
   </si>
   <si>
@@ -1738,6 +2257,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/ce29f18e8ae443bb84db0353357791af-systems-administrator-massachusetts-science-engineering-fair-cambridge</t>
   </si>
   <si>
+    <t>Tavon Learning Center Executive Director</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/839e032df6f649fda9b94311e26db636-tavon-learning-center-executive-director-clover-search-works-issaquah</t>
+  </si>
+  <si>
+    <t>Temporary Employment Attorney</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/45f2d5d1c5714ab4902a624d4e6f700a-temporary-employment-attorney-new-york-legal-assistance-group-nylag-new-york</t>
+  </si>
+  <si>
     <t>Temporary Staff Attorney, NYC</t>
   </si>
   <si>
@@ -1753,6 +2284,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/e6147be800d7451090fae998972eade6-temporary-staff-attorney-nyc-safe-passage-project-corporation-new-york</t>
   </si>
   <si>
+    <t>Trabajadora de Salud Comunitaria-Salvador Urbina</t>
+  </si>
+  <si>
+    <t>Compañeros En Salud</t>
+  </si>
+  <si>
+    <t>Salvador Urbina, Chiapas, MX</t>
+  </si>
+  <si>
+    <t>MXN 5600.00 - 5600.00/month</t>
+  </si>
+  <si>
+    <t>Health Medicine, Human Rights Civil Liberties, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7d09361e153e45839119e4734e0b4374-trabajadora-de-salud-comunitaria-salvador-urbina-companeros-en-salud-salvador-urbina</t>
+  </si>
+  <si>
+    <t>Vice President of Development</t>
+  </si>
+  <si>
+    <t>Deep South Today</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 170000.00/year</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6394bb20e08b4072bb2ef4be544b84c0-vice-president-of-development-deep-south-today-jackson</t>
+  </si>
+  <si>
     <t>Vice President of Media Engagement</t>
   </si>
   <si>
@@ -1784,6 +2348,567 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/c17d1b366c244afe9b70ba3f3a4fc99f-volunteer-and-operations-coordinator-mission-nutrition-deforest-deforest</t>
+  </si>
+  <si>
+    <t>Volunteer Coordinator</t>
+  </si>
+  <si>
+    <t>Child Creativity Lab</t>
+  </si>
+  <si>
+    <t>Santa Ana, California</t>
+  </si>
+  <si>
+    <t>USD 23.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d114042b91ec407584f0cff5a2d8f24b-volunteer-coordinator-child-creativity-lab-santa-ana</t>
+  </si>
+  <si>
+    <t>Court Appointed Special Advocates (CASA-NYC)</t>
+  </si>
+  <si>
+    <t>USD 55941.00 - 64910.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c9543d95d5da4db2937edded9c9675c4-volunteer-coordinator-court-appointed-special-advocates-casa-nyc-new-york</t>
+  </si>
+  <si>
+    <t>WEST REGION PROGRAM MANAGER / SENIOR PROGRAM MANAGER</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7025e1eff0814a60b9607833db1f7f8c-west-region-program-manager-senior-program-manager-partners-for-justice-new-york</t>
+  </si>
+  <si>
+    <t>Youth Organizer</t>
+  </si>
+  <si>
+    <t>Southeast Asian Community Alliance (SEACA)</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/09f5df19f9f04cd4a4ec8ec1be480e61-youth-organizer-southeast-asian-community-alliance-seaca-los-angeles</t>
+  </si>
+  <si>
+    <t>ASSISTANT FARM MANAGER</t>
+  </si>
+  <si>
+    <t>Veggies to Table</t>
+  </si>
+  <si>
+    <t>Newcastle, Maine</t>
+  </si>
+  <si>
+    <t>Program Operations</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73593407</t>
+  </si>
+  <si>
+    <t>BUSINESS ADMINISTRATOR</t>
+  </si>
+  <si>
+    <t>SKAGIT COUNTY - Viva Farms</t>
+  </si>
+  <si>
+    <t>Mount Vernon, Washington</t>
+  </si>
+  <si>
+    <t>Administrative</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73565301</t>
+  </si>
+  <si>
+    <t>CERTIFICATION DIRECTOR</t>
+  </si>
+  <si>
+    <t>MOSA Certified Organic</t>
+  </si>
+  <si>
+    <t>Viroqua, Wisconsin</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73617847</t>
+  </si>
+  <si>
+    <t>CHIEF ADVANCEMENT OFFICER</t>
+  </si>
+  <si>
+    <t>Hot Bread Kitchen</t>
+  </si>
+  <si>
+    <t>Fund Development</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73615403</t>
+  </si>
+  <si>
+    <t>CHIEF DEVELOPMENT OFFICER</t>
+  </si>
+  <si>
+    <t>Harlem Grown</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73616625</t>
+  </si>
+  <si>
+    <t>CHIEF EXECUTIVE OFFICER</t>
+  </si>
+  <si>
+    <t>El Pasoans Fighting Hunger Food Bank</t>
+  </si>
+  <si>
+    <t>El Paso, Texas</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73610515</t>
+  </si>
+  <si>
+    <t>COOPERATIVE DEVELOPER</t>
+  </si>
+  <si>
+    <t>Center for Community Wealth</t>
+  </si>
+  <si>
+    <t>Denver Metro, Colorado</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73579965</t>
+  </si>
+  <si>
+    <t>COORDINATOR</t>
+  </si>
+  <si>
+    <t>SUSTAINABLE FOOD GROUP - IPM Institute</t>
+  </si>
+  <si>
+    <t>Madison, Wisconsin</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73604405</t>
+  </si>
+  <si>
+    <t>CROPPING SYSTEMS COORDINATOR</t>
+  </si>
+  <si>
+    <t>Practical Farmers of Iowa</t>
+  </si>
+  <si>
+    <t>Ames, Iowa</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73590963</t>
+  </si>
+  <si>
+    <t>CULINARY MEDICINE COMMUNITY PROGRAM MANAGER</t>
+  </si>
+  <si>
+    <t>FoodShare South Carolina</t>
+  </si>
+  <si>
+    <t>Columbia, South Carolina</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73572633</t>
+  </si>
+  <si>
+    <t>CULINARY TEAM MEMBER</t>
+  </si>
+  <si>
+    <t>PART TIME AND SEASONAL - Row 7 Seed Company</t>
+  </si>
+  <si>
+    <t>Beverly, MA Framingham, MA Kansas City, MO Ann Arb</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73577521</t>
+  </si>
+  <si>
+    <t>DELIVERY DRIVER</t>
+  </si>
+  <si>
+    <t>PART TIME - Locker Project</t>
+  </si>
+  <si>
+    <t>South Portland, Maine</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73589741</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT DATA ANALYST</t>
+  </si>
+  <si>
+    <t>Gleaners Food Bank of Indiana</t>
+  </si>
+  <si>
+    <t>Indianapolis, Indiana</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73599517</t>
+  </si>
+  <si>
+    <t>DIRECTOR</t>
+  </si>
+  <si>
+    <t>TEXAS A AND M AGRILIFE FOUNDATION SEED - Texas A and M Agrilife</t>
+  </si>
+  <si>
+    <t>Vernon, Texas</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73576299</t>
+  </si>
+  <si>
+    <t>DIRECTOR AND UW EXTENSION SPECIALIST</t>
+  </si>
+  <si>
+    <t>University of Wisconsin</t>
+  </si>
+  <si>
+    <t>Stevens Point, Wisconsin</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73573855</t>
+  </si>
+  <si>
+    <t>DIRECTOR OF MARKETING AND COMMUNICATIONS</t>
+  </si>
+  <si>
+    <t>The Food Trust</t>
+  </si>
+  <si>
+    <t>Communications &amp; Outreach</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73582409</t>
+  </si>
+  <si>
+    <t>DIRECTOR OF STATE POLICY</t>
+  </si>
+  <si>
+    <t>MAZON</t>
+  </si>
+  <si>
+    <t>Hybrid in LA or DC, Washington DC</t>
+  </si>
+  <si>
+    <t>Policy &amp; Advocacy</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73608071</t>
+  </si>
+  <si>
+    <t>EXECUTIVE ASSISTANT</t>
+  </si>
+  <si>
+    <t>Marin Agricultural Land Trust</t>
+  </si>
+  <si>
+    <t>Point Reyes Station, California</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73584853</t>
+  </si>
+  <si>
+    <t>EXECUTIVE CHEF</t>
+  </si>
+  <si>
+    <t>Lowcountry Food Bank</t>
+  </si>
+  <si>
+    <t>Charleston, South Carolina</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73578743</t>
+  </si>
+  <si>
+    <t>EXECUTIVE DIRECTOR</t>
+  </si>
+  <si>
+    <t>Rolling Harvest Food Rescue</t>
+  </si>
+  <si>
+    <t>New Hope, Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73611737</t>
+  </si>
+  <si>
+    <t>FARM AND FOREST VIABILITY PROGRAM COORDINATOR</t>
+  </si>
+  <si>
+    <t>Vermont Housing and Conservation Board</t>
+  </si>
+  <si>
+    <t>Montpelier, Vermont</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73594629</t>
+  </si>
+  <si>
+    <t>FARM MANAGER</t>
+  </si>
+  <si>
+    <t>All One One All</t>
+  </si>
+  <si>
+    <t>Goshen, New York</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73567745</t>
+  </si>
+  <si>
+    <t>FINANCE DIRECTOR OF COUNTY OPERATIONS</t>
+  </si>
+  <si>
+    <t>Ohio Farm Bureau</t>
+  </si>
+  <si>
+    <t>Columbus, Ohio</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73600739</t>
+  </si>
+  <si>
+    <t>FINANCE MANAGER</t>
+  </si>
+  <si>
+    <t>Food For Others</t>
+  </si>
+  <si>
+    <t>Fairfax, Virginia</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73601961</t>
+  </si>
+  <si>
+    <t>FLORENCE URBAN HORTICULTURE AGENT</t>
+  </si>
+  <si>
+    <t>Clemson University</t>
+  </si>
+  <si>
+    <t>Florence, South Carolina</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73575077</t>
+  </si>
+  <si>
+    <t>GRANTS DEVELOPMENT ASSOCIATE</t>
+  </si>
+  <si>
+    <t>Childrens Hunger Alliance</t>
+  </si>
+  <si>
+    <t>Remote in Ohio, Ohio</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73588519</t>
+  </si>
+  <si>
+    <t>GRANTS MANAGER</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73566523</t>
+  </si>
+  <si>
+    <t>GRAPHIC DESIGNER AND PROJECT MANAGER</t>
+  </si>
+  <si>
+    <t>Bread Bakers Guild of America</t>
+  </si>
+  <si>
+    <t>Remote, Remote</t>
+  </si>
+  <si>
+    <t>Project Management</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73614181</t>
+  </si>
+  <si>
+    <t>MANAGER</t>
+  </si>
+  <si>
+    <t>FOOD SYSTEMS AND NUTRITION - Cook County Health and Hospitals System</t>
+  </si>
+  <si>
+    <t>Cook County, Illinois</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73592185</t>
+  </si>
+  <si>
+    <t>MARKETING AND COMMUNICATIONS COORDINATOR</t>
+  </si>
+  <si>
+    <t>Maple Wind Farm</t>
+  </si>
+  <si>
+    <t>Richmond, Vermont</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73612959</t>
+  </si>
+  <si>
+    <t>POULTRY MANAGEMENT EDUCATOR</t>
+  </si>
+  <si>
+    <t>Penn State</t>
+  </si>
+  <si>
+    <t>Hybrid in Lancaster County, York County, Chester C</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73605627</t>
+  </si>
+  <si>
+    <t>PRESIDENT AND CEO</t>
+  </si>
+  <si>
+    <t>FIND Food Bank</t>
+  </si>
+  <si>
+    <t>Indio, California</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73606849</t>
+  </si>
+  <si>
+    <t>PROCUREMENT MANAGER</t>
+  </si>
+  <si>
+    <t>Loaves and Fishes Community Services</t>
+  </si>
+  <si>
+    <t>Naperville, Illinois</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73586075</t>
+  </si>
+  <si>
+    <t>PRODUCE SALES ASSOCIATE</t>
+  </si>
+  <si>
+    <t>Ripe Revival</t>
+  </si>
+  <si>
+    <t>Rocky Mount, North Carolina</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Sales</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73598295</t>
+  </si>
+  <si>
+    <t>PROJECT MANAGER</t>
+  </si>
+  <si>
+    <t>TEMPORARY FULL TIME - National WIC Association</t>
+  </si>
+  <si>
+    <t>Washington DC, Washington DC</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73581187</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73603183</t>
+  </si>
+  <si>
+    <t>SEASONAL FIELD CREW</t>
+  </si>
+  <si>
+    <t>Oxbow Farm and Conservation Center</t>
+  </si>
+  <si>
+    <t>Carnation, Washington</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73587297</t>
+  </si>
+  <si>
+    <t>SENIOR DIRECTOR OF COMMUNITY ENGAGEMENT</t>
+  </si>
+  <si>
+    <t>The Nashville Food Project</t>
+  </si>
+  <si>
+    <t>Nashville, Tennessee</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73583631</t>
+  </si>
+  <si>
+    <t>SENIOR PROGRAM ASSISTANT</t>
+  </si>
+  <si>
+    <t>FOOD NUTRITION AND AGRICULTURE PROGRAM - The National Academies of Sciences Engineering and Medicine</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73568967</t>
+  </si>
+  <si>
+    <t>SPECIALIST</t>
+  </si>
+  <si>
+    <t>INSTITUTIONAL PARTNERSHIPS - Capital Area Food Bank</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73571411</t>
+  </si>
+  <si>
+    <t>TECHNICAL ASSISTANCE PROVIDER</t>
+  </si>
+  <si>
+    <t>Pasa Sustainable Agriculture</t>
+  </si>
+  <si>
+    <t>Asheville, North Carolina</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73609293</t>
+  </si>
+  <si>
+    <t>VP SALES</t>
+  </si>
+  <si>
+    <t>PRODUCE - Ripe Revival</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73595851</t>
+  </si>
+  <si>
+    <t>VALUE ADDED - Ripe Revival</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73597073</t>
+  </si>
+  <si>
+    <t>WAREHOUSE COORDINATOR</t>
+  </si>
+  <si>
+    <t>Retaaza</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73570189</t>
   </si>
 </sst>
 </file>
@@ -2987,7 +4112,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H134"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3043,257 +4168,257 @@
         <v>172</v>
       </c>
       <c r="F2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B3" t="s">
         <v>175</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>176</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E3" t="s">
         <v>177</v>
       </c>
-      <c r="D3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>178</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B4" t="s">
         <v>181</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>182</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E4" t="s">
         <v>183</v>
       </c>
-      <c r="D4" t="s">
-        <v>171</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>184</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B5" t="s">
         <v>187</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>188</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>171</v>
+      </c>
+      <c r="E5" t="s">
         <v>189</v>
       </c>
-      <c r="D5" t="s">
-        <v>171</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>190</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B6" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C6" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D6" t="s">
         <v>171</v>
       </c>
       <c r="E6" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F6" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B7" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C7" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D7" t="s">
         <v>171</v>
       </c>
       <c r="E7" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F7" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>197</v>
+      </c>
+      <c r="B8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C8" t="s">
         <v>199</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" t="s">
         <v>200</v>
       </c>
-      <c r="C8" t="s">
+      <c r="F8" t="s">
         <v>201</v>
       </c>
-      <c r="D8" t="s">
-        <v>171</v>
-      </c>
-      <c r="E8" t="s">
-        <v>202</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="H8" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>204</v>
+      </c>
+      <c r="B9" t="s">
         <v>205</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>206</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>171</v>
+      </c>
+      <c r="E9" t="s">
         <v>207</v>
       </c>
-      <c r="D9" t="s">
-        <v>171</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>208</v>
       </c>
-      <c r="F9" t="s">
+      <c r="H9" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>210</v>
+      </c>
+      <c r="B10" t="s">
         <v>211</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>212</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
+        <v>171</v>
+      </c>
+      <c r="E10" t="s">
         <v>213</v>
       </c>
-      <c r="D10" t="s">
-        <v>171</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>214</v>
       </c>
-      <c r="F10" t="s">
+      <c r="H10" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>216</v>
+      </c>
+      <c r="B11" t="s">
         <v>217</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>218</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>171</v>
+      </c>
+      <c r="E11" t="s">
         <v>219</v>
       </c>
-      <c r="D11" t="s">
-        <v>171</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
+        <v>172</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="F11" t="s">
-        <v>221</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>221</v>
+      </c>
+      <c r="B12" t="s">
+        <v>222</v>
+      </c>
+      <c r="C12" t="s">
         <v>223</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D12" t="s">
+        <v>171</v>
+      </c>
+      <c r="E12" t="s">
         <v>224</v>
       </c>
-      <c r="C12" t="s">
+      <c r="F12" t="s">
         <v>225</v>
       </c>
-      <c r="D12" t="s">
-        <v>171</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="H12" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="F12" t="s">
-        <v>227</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>227</v>
+      </c>
+      <c r="B13" t="s">
+        <v>228</v>
+      </c>
+      <c r="C13" t="s">
         <v>229</v>
       </c>
-      <c r="B13" t="s">
+      <c r="D13" t="s">
+        <v>171</v>
+      </c>
+      <c r="E13" t="s">
         <v>230</v>
-      </c>
-      <c r="C13" t="s">
-        <v>189</v>
-      </c>
-      <c r="D13" t="s">
-        <v>171</v>
-      </c>
-      <c r="E13" t="s">
-        <v>185</v>
       </c>
       <c r="F13" t="s">
         <v>231</v>
@@ -3333,364 +4458,364 @@
         <v>240</v>
       </c>
       <c r="C15" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="D15" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="E15" t="s">
         <v>242</v>
       </c>
       <c r="F15" t="s">
+        <v>172</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>244</v>
+      </c>
+      <c r="B16" t="s">
         <v>245</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>246</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E16" t="s">
         <v>247</v>
       </c>
-      <c r="D16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E16" t="s">
-        <v>185</v>
-      </c>
       <c r="F16" t="s">
-        <v>185</v>
+        <v>248</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B17" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C17" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="D17" t="s">
         <v>171</v>
       </c>
       <c r="E17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B18" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C18" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D18" t="s">
         <v>171</v>
       </c>
       <c r="E18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F18" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B19" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>189</v>
+        <v>263</v>
       </c>
       <c r="D19" t="s">
         <v>171</v>
       </c>
       <c r="E19" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F19" t="s">
-        <v>185</v>
+        <v>265</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B20" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C20" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D20" t="s">
         <v>171</v>
       </c>
       <c r="E20" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F20" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B21" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C21" t="s">
-        <v>272</v>
+        <v>199</v>
       </c>
       <c r="D21" t="s">
         <v>171</v>
       </c>
       <c r="E21" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="F21" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B22" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C22" t="s">
-        <v>219</v>
+        <v>279</v>
       </c>
       <c r="D22" t="s">
         <v>171</v>
       </c>
       <c r="E22" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="F22" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>64</v>
+        <v>283</v>
       </c>
       <c r="B23" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C23" t="s">
-        <v>280</v>
+        <v>182</v>
       </c>
       <c r="D23" t="s">
-        <v>171</v>
+        <v>285</v>
       </c>
       <c r="E23" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="F23" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B24" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C24" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>171</v>
       </c>
       <c r="E24" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="F24" t="s">
-        <v>179</v>
+        <v>293</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B25" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C25" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="D25" t="s">
         <v>171</v>
       </c>
       <c r="E25" t="s">
-        <v>293</v>
+        <v>172</v>
       </c>
       <c r="F25" t="s">
-        <v>294</v>
+        <v>172</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B26" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C26" t="s">
-        <v>298</v>
+        <v>199</v>
       </c>
       <c r="D26" t="s">
         <v>171</v>
       </c>
       <c r="E26" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="F26" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B27" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C27" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D27" t="s">
         <v>171</v>
       </c>
       <c r="E27" t="s">
-        <v>257</v>
+        <v>307</v>
       </c>
       <c r="F27" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B28" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C28" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="D28" t="s">
         <v>171</v>
       </c>
       <c r="E28" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F28" t="s">
-        <v>309</v>
+        <v>172</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B29" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C29" t="s">
-        <v>219</v>
+        <v>316</v>
       </c>
       <c r="D29" t="s">
         <v>171</v>
       </c>
       <c r="E29" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F29" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B30" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C30" t="s">
-        <v>189</v>
+        <v>322</v>
       </c>
       <c r="D30" t="s">
         <v>171</v>
       </c>
       <c r="E30" t="s">
-        <v>276</v>
+        <v>172</v>
       </c>
       <c r="F30" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -3698,160 +4823,160 @@
         <v>320</v>
       </c>
       <c r="B31" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C31" t="s">
-        <v>322</v>
+        <v>182</v>
       </c>
       <c r="D31" t="s">
         <v>171</v>
       </c>
       <c r="E31" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F31" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>326</v>
+        <v>64</v>
       </c>
       <c r="B32" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C32" t="s">
-        <v>177</v>
+        <v>330</v>
       </c>
       <c r="D32" t="s">
         <v>171</v>
       </c>
       <c r="E32" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F32" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B33" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C33" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="D33" t="s">
-        <v>171</v>
+        <v>337</v>
       </c>
       <c r="E33" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="F33" t="s">
-        <v>335</v>
+        <v>190</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B34" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C34" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D34" t="s">
         <v>171</v>
       </c>
       <c r="E34" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F34" t="s">
-        <v>185</v>
+        <v>344</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B35" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C35" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D35" t="s">
         <v>171</v>
       </c>
       <c r="E35" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="F35" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="B36" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C36" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="D36" t="s">
         <v>171</v>
       </c>
       <c r="E36" t="s">
-        <v>349</v>
+        <v>317</v>
       </c>
       <c r="F36" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B37" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C37" t="s">
-        <v>219</v>
+        <v>358</v>
       </c>
       <c r="D37" t="s">
         <v>171</v>
       </c>
       <c r="E37" t="s">
-        <v>276</v>
+        <v>307</v>
       </c>
       <c r="F37" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -3859,42 +4984,42 @@
         <v>356</v>
       </c>
       <c r="B38" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C38" t="s">
-        <v>358</v>
+        <v>279</v>
       </c>
       <c r="D38" t="s">
-        <v>359</v>
+        <v>171</v>
       </c>
       <c r="E38" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F38" t="s">
-        <v>361</v>
+        <v>172</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="B39" t="s">
         <v>364</v>
       </c>
       <c r="C39" t="s">
+        <v>182</v>
+      </c>
+      <c r="D39" t="s">
+        <v>171</v>
+      </c>
+      <c r="E39" t="s">
         <v>365</v>
       </c>
-      <c r="D39" t="s">
-        <v>171</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>366</v>
-      </c>
-      <c r="F39" t="s">
-        <v>209</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>367</v>
@@ -3908,7 +5033,7 @@
         <v>369</v>
       </c>
       <c r="C40" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="D40" t="s">
         <v>171</v>
@@ -3917,1137 +5042,2172 @@
         <v>370</v>
       </c>
       <c r="F40" t="s">
+        <v>172</v>
+      </c>
+      <c r="H40" s="2" t="s">
         <v>371</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B41" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C41" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D41" t="s">
         <v>171</v>
       </c>
       <c r="E41" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="F41" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B42" t="s">
-        <v>250</v>
+        <v>379</v>
       </c>
       <c r="C42" t="s">
-        <v>189</v>
+        <v>380</v>
       </c>
       <c r="D42" t="s">
         <v>171</v>
       </c>
       <c r="E42" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F42" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B43" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C43" t="s">
-        <v>381</v>
+        <v>182</v>
       </c>
       <c r="D43" t="s">
         <v>171</v>
       </c>
       <c r="E43" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F43" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B44" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C44" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="D44" t="s">
         <v>171</v>
       </c>
       <c r="E44" t="s">
-        <v>293</v>
+        <v>391</v>
       </c>
       <c r="F44" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B45" t="s">
-        <v>224</v>
+        <v>395</v>
       </c>
       <c r="C45" t="s">
-        <v>225</v>
+        <v>182</v>
       </c>
       <c r="D45" t="s">
         <v>171</v>
       </c>
       <c r="E45" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="F45" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="B46" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="C46" t="s">
-        <v>219</v>
+        <v>257</v>
       </c>
       <c r="D46" t="s">
         <v>171</v>
       </c>
       <c r="E46" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="F46" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="B47" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="C47" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="D47" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="E47" t="s">
-        <v>400</v>
+        <v>326</v>
       </c>
       <c r="F47" t="s">
-        <v>237</v>
+        <v>406</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="B48" t="s">
-        <v>327</v>
+        <v>409</v>
       </c>
       <c r="C48" t="s">
-        <v>177</v>
+        <v>410</v>
       </c>
       <c r="D48" t="s">
         <v>171</v>
       </c>
       <c r="E48" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="F48" t="s">
-        <v>329</v>
+        <v>412</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="B49" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="C49" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="D49" t="s">
-        <v>408</v>
+        <v>171</v>
       </c>
       <c r="E49" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="F49" t="s">
-        <v>215</v>
+        <v>418</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="B50" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="C50" t="s">
-        <v>219</v>
+        <v>188</v>
       </c>
       <c r="D50" t="s">
         <v>171</v>
       </c>
       <c r="E50" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="F50" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="B51" t="s">
-        <v>369</v>
+        <v>426</v>
       </c>
       <c r="C51" t="s">
-        <v>373</v>
+        <v>427</v>
       </c>
       <c r="D51" t="s">
         <v>171</v>
       </c>
       <c r="E51" t="s">
-        <v>366</v>
+        <v>428</v>
       </c>
       <c r="F51" t="s">
-        <v>371</v>
+        <v>429</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="B52" t="s">
-        <v>419</v>
+        <v>240</v>
       </c>
       <c r="C52" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="D52" t="s">
-        <v>287</v>
+        <v>171</v>
       </c>
       <c r="E52" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="F52" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="B53" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="C53" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="D53" t="s">
         <v>171</v>
       </c>
       <c r="E53" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="F53" t="s">
-        <v>185</v>
+        <v>438</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B54" t="s">
-        <v>424</v>
+        <v>440</v>
       </c>
       <c r="C54" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="D54" t="s">
         <v>171</v>
       </c>
       <c r="E54" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="F54" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B55" t="s">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="C55" t="s">
-        <v>434</v>
+        <v>182</v>
       </c>
       <c r="D55" t="s">
         <v>171</v>
       </c>
       <c r="E55" t="s">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="F55" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="B56" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="C56" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="D56" t="s">
         <v>171</v>
       </c>
       <c r="E56" t="s">
-        <v>440</v>
+        <v>172</v>
       </c>
       <c r="F56" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="B57" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="C57" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="D57" t="s">
-        <v>408</v>
+        <v>171</v>
       </c>
       <c r="E57" t="s">
-        <v>446</v>
+        <v>219</v>
       </c>
       <c r="F57" t="s">
-        <v>185</v>
+        <v>456</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="B58" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="C58" t="s">
-        <v>177</v>
+        <v>460</v>
       </c>
       <c r="D58" t="s">
-        <v>171</v>
+        <v>461</v>
       </c>
       <c r="E58" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="F58" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="B59" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="C59" t="s">
-        <v>455</v>
+        <v>182</v>
       </c>
       <c r="D59" t="s">
         <v>171</v>
       </c>
       <c r="E59" t="s">
-        <v>456</v>
+        <v>326</v>
       </c>
       <c r="F59" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="B60" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="C60" t="s">
-        <v>373</v>
+        <v>471</v>
       </c>
       <c r="D60" t="s">
-        <v>171</v>
+        <v>461</v>
       </c>
       <c r="E60" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="F60" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="B61" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="C61" t="s">
-        <v>292</v>
+        <v>477</v>
       </c>
       <c r="D61" t="s">
         <v>171</v>
       </c>
       <c r="E61" t="s">
-        <v>334</v>
+        <v>478</v>
       </c>
       <c r="F61" t="s">
-        <v>466</v>
+        <v>237</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="B62" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="C62" t="s">
-        <v>292</v>
+        <v>482</v>
       </c>
       <c r="D62" t="s">
         <v>171</v>
       </c>
       <c r="E62" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="F62" t="s">
-        <v>185</v>
+        <v>484</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>471</v>
+        <v>485</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>472</v>
+        <v>486</v>
       </c>
       <c r="B63" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="C63" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="D63" t="s">
         <v>171</v>
       </c>
       <c r="E63" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="F63" t="s">
-        <v>215</v>
+        <v>489</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>475</v>
+        <v>490</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="B64" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="C64" t="s">
-        <v>478</v>
+        <v>491</v>
       </c>
       <c r="D64" t="s">
         <v>171</v>
       </c>
       <c r="E64" t="s">
-        <v>226</v>
+        <v>488</v>
       </c>
       <c r="F64" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="B65" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="C65" t="s">
-        <v>483</v>
+        <v>342</v>
       </c>
       <c r="D65" t="s">
         <v>171</v>
       </c>
       <c r="E65" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="F65" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="B66" t="s">
-        <v>488</v>
+        <v>300</v>
       </c>
       <c r="C66" t="s">
-        <v>489</v>
+        <v>199</v>
       </c>
       <c r="D66" t="s">
         <v>171</v>
       </c>
       <c r="E66" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="F66" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="B67" t="s">
-        <v>261</v>
+        <v>503</v>
       </c>
       <c r="C67" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="D67" t="s">
         <v>171</v>
       </c>
       <c r="E67" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="F67" t="s">
-        <v>185</v>
+        <v>506</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="B68" t="s">
-        <v>261</v>
+        <v>509</v>
       </c>
       <c r="C68" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="D68" t="s">
         <v>171</v>
       </c>
       <c r="E68" t="s">
-        <v>495</v>
+        <v>343</v>
       </c>
       <c r="F68" t="s">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>498</v>
+        <v>511</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>499</v>
+        <v>512</v>
       </c>
       <c r="B69" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C69" t="s">
-        <v>500</v>
+        <v>263</v>
       </c>
       <c r="D69" t="s">
         <v>171</v>
       </c>
       <c r="E69" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="F69" t="s">
-        <v>185</v>
+        <v>514</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>501</v>
+        <v>515</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="B70" t="s">
-        <v>503</v>
+        <v>517</v>
       </c>
       <c r="C70" t="s">
-        <v>504</v>
+        <v>182</v>
       </c>
       <c r="D70" t="s">
-        <v>287</v>
+        <v>171</v>
       </c>
       <c r="E70" t="s">
-        <v>505</v>
+        <v>518</v>
       </c>
       <c r="F70" t="s">
-        <v>506</v>
+        <v>519</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>507</v>
+        <v>520</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>508</v>
+        <v>521</v>
       </c>
       <c r="B71" t="s">
-        <v>327</v>
+        <v>522</v>
       </c>
       <c r="C71" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="D71" t="s">
-        <v>171</v>
+        <v>285</v>
       </c>
       <c r="E71" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="F71" t="s">
-        <v>329</v>
+        <v>281</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>510</v>
+        <v>524</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>511</v>
+        <v>525</v>
       </c>
       <c r="B72" t="s">
-        <v>185</v>
+        <v>421</v>
       </c>
       <c r="C72" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D72" t="s">
         <v>171</v>
       </c>
       <c r="E72" t="s">
-        <v>197</v>
+        <v>526</v>
       </c>
       <c r="F72" t="s">
-        <v>512</v>
+        <v>423</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>513</v>
+        <v>527</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>514</v>
+        <v>528</v>
       </c>
       <c r="B73" t="s">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="C73" t="s">
-        <v>343</v>
+        <v>530</v>
       </c>
       <c r="D73" t="s">
-        <v>171</v>
+        <v>531</v>
       </c>
       <c r="E73" t="s">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="F73" t="s">
-        <v>517</v>
+        <v>248</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>518</v>
+        <v>533</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>519</v>
+        <v>534</v>
       </c>
       <c r="B74" t="s">
-        <v>520</v>
+        <v>535</v>
       </c>
       <c r="C74" t="s">
-        <v>521</v>
+        <v>188</v>
       </c>
       <c r="D74" t="s">
         <v>171</v>
       </c>
       <c r="E74" t="s">
-        <v>344</v>
+        <v>536</v>
       </c>
       <c r="F74" t="s">
-        <v>185</v>
+        <v>537</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>522</v>
+        <v>538</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>523</v>
+        <v>539</v>
       </c>
       <c r="B75" t="s">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="C75" t="s">
-        <v>525</v>
+        <v>182</v>
       </c>
       <c r="D75" t="s">
         <v>171</v>
       </c>
       <c r="E75" t="s">
-        <v>526</v>
+        <v>381</v>
       </c>
       <c r="F75" t="s">
-        <v>527</v>
+        <v>541</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>528</v>
+        <v>542</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>529</v>
+        <v>543</v>
       </c>
       <c r="B76" t="s">
-        <v>530</v>
+        <v>487</v>
       </c>
       <c r="C76" t="s">
-        <v>256</v>
+        <v>491</v>
       </c>
       <c r="D76" t="s">
         <v>171</v>
       </c>
       <c r="E76" t="s">
-        <v>531</v>
+        <v>478</v>
       </c>
       <c r="F76" t="s">
-        <v>532</v>
+        <v>489</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>533</v>
+        <v>544</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="B77" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="C77" t="s">
-        <v>536</v>
+        <v>547</v>
       </c>
       <c r="D77" t="s">
-        <v>171</v>
+        <v>337</v>
       </c>
       <c r="E77" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="F77" t="s">
-        <v>538</v>
+        <v>172</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>539</v>
+        <v>549</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="B78" t="s">
-        <v>541</v>
+        <v>551</v>
       </c>
       <c r="C78" t="s">
-        <v>219</v>
+        <v>552</v>
       </c>
       <c r="D78" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="E78" t="s">
-        <v>542</v>
+        <v>553</v>
       </c>
       <c r="F78" t="s">
-        <v>543</v>
+        <v>172</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>544</v>
+        <v>554</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>545</v>
+        <v>555</v>
       </c>
       <c r="B79" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C79" t="s">
-        <v>489</v>
+        <v>556</v>
       </c>
       <c r="D79" t="s">
         <v>171</v>
       </c>
       <c r="E79" t="s">
-        <v>547</v>
+        <v>557</v>
       </c>
       <c r="F79" t="s">
-        <v>191</v>
+        <v>558</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>548</v>
+        <v>559</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="B80" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C80" t="s">
-        <v>551</v>
+        <v>561</v>
       </c>
       <c r="D80" t="s">
         <v>171</v>
       </c>
       <c r="E80" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F80" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>554</v>
+        <v>563</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>549</v>
+        <v>564</v>
       </c>
       <c r="B81" t="s">
-        <v>550</v>
+        <v>565</v>
       </c>
       <c r="C81" t="s">
-        <v>555</v>
+        <v>566</v>
       </c>
       <c r="D81" t="s">
         <v>171</v>
       </c>
       <c r="E81" t="s">
-        <v>552</v>
+        <v>224</v>
       </c>
       <c r="F81" t="s">
-        <v>553</v>
+        <v>567</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>549</v>
+        <v>569</v>
       </c>
       <c r="B82" t="s">
-        <v>550</v>
+        <v>570</v>
       </c>
       <c r="C82" t="s">
-        <v>557</v>
+        <v>571</v>
       </c>
       <c r="D82" t="s">
-        <v>171</v>
+        <v>461</v>
       </c>
       <c r="E82" t="s">
-        <v>552</v>
+        <v>572</v>
       </c>
       <c r="F82" t="s">
-        <v>553</v>
+        <v>573</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>558</v>
+        <v>574</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>549</v>
+        <v>575</v>
       </c>
       <c r="B83" t="s">
-        <v>279</v>
+        <v>576</v>
       </c>
       <c r="C83" t="s">
-        <v>280</v>
+        <v>577</v>
       </c>
       <c r="D83" t="s">
-        <v>171</v>
+        <v>531</v>
       </c>
       <c r="E83" t="s">
-        <v>559</v>
+        <v>578</v>
       </c>
       <c r="F83" t="s">
-        <v>282</v>
+        <v>172</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>560</v>
+        <v>579</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>561</v>
+        <v>580</v>
       </c>
       <c r="B84" t="s">
-        <v>562</v>
+        <v>581</v>
       </c>
       <c r="C84" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D84" t="s">
         <v>171</v>
       </c>
       <c r="E84" t="s">
-        <v>563</v>
+        <v>582</v>
       </c>
       <c r="F84" t="s">
-        <v>203</v>
+        <v>583</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>564</v>
+        <v>584</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>565</v>
+        <v>585</v>
       </c>
       <c r="B85" t="s">
-        <v>200</v>
+        <v>586</v>
       </c>
       <c r="C85" t="s">
-        <v>201</v>
+        <v>374</v>
       </c>
       <c r="D85" t="s">
         <v>171</v>
       </c>
       <c r="E85" t="s">
-        <v>566</v>
+        <v>587</v>
       </c>
       <c r="F85" t="s">
-        <v>567</v>
+        <v>588</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>568</v>
+        <v>589</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>569</v>
+        <v>590</v>
       </c>
       <c r="B86" t="s">
-        <v>570</v>
+        <v>591</v>
       </c>
       <c r="C86" t="s">
-        <v>272</v>
+        <v>491</v>
       </c>
       <c r="D86" t="s">
         <v>171</v>
       </c>
       <c r="E86" t="s">
-        <v>571</v>
+        <v>592</v>
       </c>
       <c r="F86" t="s">
-        <v>572</v>
+        <v>593</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>573</v>
+        <v>594</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>574</v>
+        <v>595</v>
       </c>
       <c r="B87" t="s">
-        <v>575</v>
+        <v>596</v>
       </c>
       <c r="C87" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="D87" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="E87" t="s">
-        <v>576</v>
+        <v>597</v>
       </c>
       <c r="F87" t="s">
-        <v>577</v>
+        <v>402</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>578</v>
+        <v>598</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>579</v>
+        <v>599</v>
       </c>
       <c r="B88" t="s">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="C88" t="s">
-        <v>292</v>
+        <v>342</v>
       </c>
       <c r="D88" t="s">
         <v>171</v>
       </c>
       <c r="E88" t="s">
-        <v>581</v>
+        <v>428</v>
       </c>
       <c r="F88" t="s">
-        <v>582</v>
+        <v>601</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>583</v>
+        <v>602</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>584</v>
+        <v>603</v>
       </c>
       <c r="B89" t="s">
-        <v>585</v>
+        <v>205</v>
       </c>
       <c r="C89" t="s">
-        <v>586</v>
+        <v>206</v>
       </c>
       <c r="D89" t="s">
-        <v>359</v>
+        <v>171</v>
       </c>
       <c r="E89" t="s">
-        <v>587</v>
+        <v>224</v>
       </c>
       <c r="F89" t="s">
-        <v>588</v>
+        <v>429</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>589</v>
+        <v>604</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>605</v>
+      </c>
+      <c r="B90" t="s">
+        <v>205</v>
+      </c>
+      <c r="C90" t="s">
+        <v>206</v>
+      </c>
+      <c r="D90" t="s">
+        <v>171</v>
+      </c>
+      <c r="E90" t="s">
+        <v>606</v>
+      </c>
+      <c r="F90" t="s">
+        <v>429</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>608</v>
+      </c>
+      <c r="B91" t="s">
+        <v>609</v>
+      </c>
+      <c r="C91" t="s">
+        <v>342</v>
+      </c>
+      <c r="D91" t="s">
+        <v>171</v>
+      </c>
+      <c r="E91" t="s">
+        <v>610</v>
+      </c>
+      <c r="F91" t="s">
+        <v>172</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>612</v>
+      </c>
+      <c r="B92" t="s">
+        <v>613</v>
+      </c>
+      <c r="C92" t="s">
+        <v>342</v>
+      </c>
+      <c r="D92" t="s">
+        <v>171</v>
+      </c>
+      <c r="E92" t="s">
+        <v>614</v>
+      </c>
+      <c r="F92" t="s">
+        <v>248</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>616</v>
+      </c>
+      <c r="B93" t="s">
+        <v>617</v>
+      </c>
+      <c r="C93" t="s">
+        <v>182</v>
+      </c>
+      <c r="D93" t="s">
+        <v>171</v>
+      </c>
+      <c r="E93" t="s">
+        <v>618</v>
+      </c>
+      <c r="F93" t="s">
+        <v>172</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>620</v>
+      </c>
+      <c r="B94" t="s">
+        <v>621</v>
+      </c>
+      <c r="C94" t="s">
+        <v>218</v>
+      </c>
+      <c r="D94" t="s">
+        <v>171</v>
+      </c>
+      <c r="E94" t="s">
+        <v>622</v>
+      </c>
+      <c r="F94" t="s">
+        <v>623</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>625</v>
+      </c>
+      <c r="B95" t="s">
+        <v>626</v>
+      </c>
+      <c r="C95" t="s">
+        <v>627</v>
+      </c>
+      <c r="D95" t="s">
+        <v>171</v>
+      </c>
+      <c r="E95" t="s">
+        <v>264</v>
+      </c>
+      <c r="F95" t="s">
+        <v>628</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>630</v>
+      </c>
+      <c r="B96" t="s">
+        <v>631</v>
+      </c>
+      <c r="C96" t="s">
+        <v>632</v>
+      </c>
+      <c r="D96" t="s">
+        <v>171</v>
+      </c>
+      <c r="E96" t="s">
+        <v>633</v>
+      </c>
+      <c r="F96" t="s">
+        <v>634</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>636</v>
+      </c>
+      <c r="B97" t="s">
+        <v>637</v>
+      </c>
+      <c r="C97" t="s">
+        <v>638</v>
+      </c>
+      <c r="D97" t="s">
+        <v>171</v>
+      </c>
+      <c r="E97" t="s">
+        <v>639</v>
+      </c>
+      <c r="F97" t="s">
+        <v>640</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>642</v>
+      </c>
+      <c r="B98" t="s">
+        <v>311</v>
+      </c>
+      <c r="C98" t="s">
+        <v>643</v>
+      </c>
+      <c r="D98" t="s">
+        <v>171</v>
+      </c>
+      <c r="E98" t="s">
+        <v>644</v>
+      </c>
+      <c r="F98" t="s">
+        <v>172</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>646</v>
+      </c>
+      <c r="B99" t="s">
+        <v>311</v>
+      </c>
+      <c r="C99" t="s">
+        <v>199</v>
+      </c>
+      <c r="D99" t="s">
+        <v>171</v>
+      </c>
+      <c r="E99" t="s">
+        <v>644</v>
+      </c>
+      <c r="F99" t="s">
+        <v>172</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>648</v>
+      </c>
+      <c r="B100" t="s">
+        <v>311</v>
+      </c>
+      <c r="C100" t="s">
+        <v>649</v>
+      </c>
+      <c r="D100" t="s">
+        <v>171</v>
+      </c>
+      <c r="E100" t="s">
+        <v>644</v>
+      </c>
+      <c r="F100" t="s">
+        <v>172</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>651</v>
+      </c>
+      <c r="B101" t="s">
+        <v>652</v>
+      </c>
+      <c r="C101" t="s">
+        <v>653</v>
+      </c>
+      <c r="D101" t="s">
+        <v>337</v>
+      </c>
+      <c r="E101" t="s">
+        <v>654</v>
+      </c>
+      <c r="F101" t="s">
+        <v>655</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>657</v>
+      </c>
+      <c r="B102" t="s">
+        <v>658</v>
+      </c>
+      <c r="C102" t="s">
+        <v>659</v>
+      </c>
+      <c r="D102" t="s">
+        <v>337</v>
+      </c>
+      <c r="E102" t="s">
+        <v>660</v>
+      </c>
+      <c r="F102" t="s">
+        <v>661</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>663</v>
+      </c>
+      <c r="B103" t="s">
+        <v>664</v>
+      </c>
+      <c r="C103" t="s">
+        <v>374</v>
+      </c>
+      <c r="D103" t="s">
+        <v>171</v>
+      </c>
+      <c r="E103" t="s">
+        <v>665</v>
+      </c>
+      <c r="F103" t="s">
+        <v>666</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>668</v>
+      </c>
+      <c r="B104" t="s">
+        <v>421</v>
+      </c>
+      <c r="C104" t="s">
+        <v>188</v>
+      </c>
+      <c r="D104" t="s">
+        <v>171</v>
+      </c>
+      <c r="E104" t="s">
+        <v>669</v>
+      </c>
+      <c r="F104" t="s">
+        <v>423</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>671</v>
+      </c>
+      <c r="B105" t="s">
+        <v>672</v>
+      </c>
+      <c r="C105" t="s">
+        <v>673</v>
+      </c>
+      <c r="D105" t="s">
+        <v>285</v>
+      </c>
+      <c r="E105" t="s">
+        <v>674</v>
+      </c>
+      <c r="F105" t="s">
+        <v>675</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>677</v>
+      </c>
+      <c r="B106" t="s">
+        <v>172</v>
+      </c>
+      <c r="C106" t="s">
+        <v>199</v>
+      </c>
+      <c r="D106" t="s">
+        <v>171</v>
+      </c>
+      <c r="E106" t="s">
+        <v>219</v>
+      </c>
+      <c r="F106" t="s">
+        <v>678</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>680</v>
+      </c>
+      <c r="B107" t="s">
+        <v>681</v>
+      </c>
+      <c r="C107" t="s">
+        <v>436</v>
+      </c>
+      <c r="D107" t="s">
+        <v>171</v>
+      </c>
+      <c r="E107" t="s">
+        <v>682</v>
+      </c>
+      <c r="F107" t="s">
+        <v>683</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>685</v>
+      </c>
+      <c r="B108" t="s">
+        <v>686</v>
+      </c>
+      <c r="C108" t="s">
+        <v>291</v>
+      </c>
+      <c r="D108" t="s">
+        <v>171</v>
+      </c>
+      <c r="E108" t="s">
+        <v>437</v>
+      </c>
+      <c r="F108" t="s">
+        <v>172</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>688</v>
+      </c>
+      <c r="B109" t="s">
+        <v>689</v>
+      </c>
+      <c r="C109" t="s">
+        <v>690</v>
+      </c>
+      <c r="D109" t="s">
+        <v>171</v>
+      </c>
+      <c r="E109" t="s">
+        <v>691</v>
+      </c>
+      <c r="F109" t="s">
+        <v>692</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>694</v>
+      </c>
+      <c r="B110" t="s">
+        <v>695</v>
+      </c>
+      <c r="C110" t="s">
+        <v>306</v>
+      </c>
+      <c r="D110" t="s">
+        <v>171</v>
+      </c>
+      <c r="E110" t="s">
+        <v>696</v>
+      </c>
+      <c r="F110" t="s">
+        <v>412</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>698</v>
+      </c>
+      <c r="B111" t="s">
+        <v>699</v>
+      </c>
+      <c r="C111" t="s">
+        <v>700</v>
+      </c>
+      <c r="D111" t="s">
+        <v>171</v>
+      </c>
+      <c r="E111" t="s">
+        <v>701</v>
+      </c>
+      <c r="F111" t="s">
+        <v>702</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>704</v>
+      </c>
+      <c r="B112" t="s">
+        <v>705</v>
+      </c>
+      <c r="C112" t="s">
+        <v>182</v>
+      </c>
+      <c r="D112" t="s">
+        <v>285</v>
+      </c>
+      <c r="E112" t="s">
+        <v>706</v>
+      </c>
+      <c r="F112" t="s">
+        <v>707</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>709</v>
+      </c>
+      <c r="B113" t="s">
+        <v>710</v>
+      </c>
+      <c r="C113" t="s">
+        <v>638</v>
+      </c>
+      <c r="D113" t="s">
+        <v>171</v>
+      </c>
+      <c r="E113" t="s">
+        <v>711</v>
+      </c>
+      <c r="F113" t="s">
+        <v>201</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>713</v>
+      </c>
+      <c r="B114" t="s">
+        <v>714</v>
+      </c>
+      <c r="C114" t="s">
+        <v>715</v>
+      </c>
+      <c r="D114" t="s">
+        <v>171</v>
+      </c>
+      <c r="E114" t="s">
+        <v>716</v>
+      </c>
+      <c r="F114" t="s">
+        <v>717</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>713</v>
+      </c>
+      <c r="B115" t="s">
+        <v>714</v>
+      </c>
+      <c r="C115" t="s">
+        <v>719</v>
+      </c>
+      <c r="D115" t="s">
+        <v>171</v>
+      </c>
+      <c r="E115" t="s">
+        <v>716</v>
+      </c>
+      <c r="F115" t="s">
+        <v>717</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>713</v>
+      </c>
+      <c r="B116" t="s">
+        <v>714</v>
+      </c>
+      <c r="C116" t="s">
+        <v>721</v>
+      </c>
+      <c r="D116" t="s">
+        <v>171</v>
+      </c>
+      <c r="E116" t="s">
+        <v>716</v>
+      </c>
+      <c r="F116" t="s">
+        <v>717</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>713</v>
+      </c>
+      <c r="B117" t="s">
+        <v>329</v>
+      </c>
+      <c r="C117" t="s">
+        <v>330</v>
+      </c>
+      <c r="D117" t="s">
+        <v>171</v>
+      </c>
+      <c r="E117" t="s">
+        <v>723</v>
+      </c>
+      <c r="F117" t="s">
+        <v>332</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>725</v>
+      </c>
+      <c r="B118" t="s">
+        <v>726</v>
+      </c>
+      <c r="C118" t="s">
+        <v>199</v>
+      </c>
+      <c r="D118" t="s">
+        <v>171</v>
+      </c>
+      <c r="E118" t="s">
+        <v>727</v>
+      </c>
+      <c r="F118" t="s">
+        <v>201</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>729</v>
+      </c>
+      <c r="B119" t="s">
+        <v>726</v>
+      </c>
+      <c r="C119" t="s">
+        <v>199</v>
+      </c>
+      <c r="D119" t="s">
+        <v>171</v>
+      </c>
+      <c r="E119" t="s">
+        <v>727</v>
+      </c>
+      <c r="F119" t="s">
+        <v>201</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>731</v>
+      </c>
+      <c r="B120" t="s">
+        <v>726</v>
+      </c>
+      <c r="C120" t="s">
+        <v>199</v>
+      </c>
+      <c r="D120" t="s">
+        <v>171</v>
+      </c>
+      <c r="E120" t="s">
+        <v>732</v>
+      </c>
+      <c r="F120" t="s">
+        <v>201</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>734</v>
+      </c>
+      <c r="B121" t="s">
+        <v>735</v>
+      </c>
+      <c r="C121" t="s">
+        <v>199</v>
+      </c>
+      <c r="D121" t="s">
+        <v>171</v>
+      </c>
+      <c r="E121" t="s">
+        <v>736</v>
+      </c>
+      <c r="F121" t="s">
+        <v>231</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>738</v>
+      </c>
+      <c r="B122" t="s">
+        <v>228</v>
+      </c>
+      <c r="C122" t="s">
+        <v>229</v>
+      </c>
+      <c r="D122" t="s">
+        <v>171</v>
+      </c>
+      <c r="E122" t="s">
+        <v>739</v>
+      </c>
+      <c r="F122" t="s">
+        <v>740</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>742</v>
+      </c>
+      <c r="B123" t="s">
+        <v>743</v>
+      </c>
+      <c r="C123" t="s">
+        <v>322</v>
+      </c>
+      <c r="D123" t="s">
+        <v>171</v>
+      </c>
+      <c r="E123" t="s">
+        <v>744</v>
+      </c>
+      <c r="F123" t="s">
+        <v>745</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>747</v>
+      </c>
+      <c r="B124" t="s">
+        <v>240</v>
+      </c>
+      <c r="C124" t="s">
+        <v>432</v>
+      </c>
+      <c r="D124" t="s">
+        <v>171</v>
+      </c>
+      <c r="E124" t="s">
+        <v>433</v>
+      </c>
+      <c r="F124" t="s">
+        <v>172</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>749</v>
+      </c>
+      <c r="B125" t="s">
+        <v>726</v>
+      </c>
+      <c r="C125" t="s">
+        <v>199</v>
+      </c>
+      <c r="D125" t="s">
+        <v>171</v>
+      </c>
+      <c r="E125" t="s">
+        <v>727</v>
+      </c>
+      <c r="F125" t="s">
+        <v>201</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>751</v>
+      </c>
+      <c r="B126" t="s">
+        <v>752</v>
+      </c>
+      <c r="C126" t="s">
+        <v>199</v>
+      </c>
+      <c r="D126" t="s">
+        <v>285</v>
+      </c>
+      <c r="E126" t="s">
+        <v>753</v>
+      </c>
+      <c r="F126" t="s">
+        <v>754</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>756</v>
+      </c>
+      <c r="B127" t="s">
+        <v>757</v>
+      </c>
+      <c r="C127" t="s">
+        <v>758</v>
+      </c>
+      <c r="D127" t="s">
+        <v>531</v>
+      </c>
+      <c r="E127" t="s">
+        <v>759</v>
+      </c>
+      <c r="F127" t="s">
+        <v>760</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>762</v>
+      </c>
+      <c r="B128" t="s">
+        <v>763</v>
+      </c>
+      <c r="C128" t="s">
+        <v>182</v>
+      </c>
+      <c r="D128" t="s">
+        <v>171</v>
+      </c>
+      <c r="E128" t="s">
+        <v>764</v>
+      </c>
+      <c r="F128" t="s">
+        <v>765</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>767</v>
+      </c>
+      <c r="B129" t="s">
+        <v>768</v>
+      </c>
+      <c r="C129" t="s">
+        <v>342</v>
+      </c>
+      <c r="D129" t="s">
+        <v>171</v>
+      </c>
+      <c r="E129" t="s">
+        <v>769</v>
+      </c>
+      <c r="F129" t="s">
+        <v>770</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>772</v>
+      </c>
+      <c r="B130" t="s">
+        <v>773</v>
+      </c>
+      <c r="C130" t="s">
+        <v>774</v>
+      </c>
+      <c r="D130" t="s">
+        <v>461</v>
+      </c>
+      <c r="E130" t="s">
+        <v>775</v>
+      </c>
+      <c r="F130" t="s">
+        <v>776</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>778</v>
+      </c>
+      <c r="B131" t="s">
+        <v>779</v>
+      </c>
+      <c r="C131" t="s">
+        <v>780</v>
+      </c>
+      <c r="D131" t="s">
+        <v>337</v>
+      </c>
+      <c r="E131" t="s">
+        <v>781</v>
+      </c>
+      <c r="F131" t="s">
+        <v>782</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>778</v>
+      </c>
+      <c r="B132" t="s">
+        <v>784</v>
+      </c>
+      <c r="C132" t="s">
+        <v>199</v>
+      </c>
+      <c r="D132" t="s">
+        <v>171</v>
+      </c>
+      <c r="E132" t="s">
+        <v>785</v>
+      </c>
+      <c r="F132" t="s">
+        <v>786</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>788</v>
+      </c>
+      <c r="B133" t="s">
+        <v>664</v>
+      </c>
+      <c r="C133" t="s">
+        <v>789</v>
+      </c>
+      <c r="D133" t="s">
+        <v>171</v>
+      </c>
+      <c r="E133" t="s">
+        <v>790</v>
+      </c>
+      <c r="F133" t="s">
+        <v>666</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>792</v>
+      </c>
+      <c r="B134" t="s">
+        <v>793</v>
+      </c>
+      <c r="C134" t="s">
+        <v>374</v>
+      </c>
+      <c r="D134" t="s">
+        <v>171</v>
+      </c>
+      <c r="E134" t="s">
+        <v>794</v>
+      </c>
+      <c r="F134" t="s">
+        <v>484</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>795</v>
       </c>
     </row>
   </sheetData>
@@ -5141,6 +7301,51 @@
     <hyperlink ref="H87" r:id="rId86"/>
     <hyperlink ref="H88" r:id="rId87"/>
     <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -5149,7 +7354,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -5188,8 +7393,1066 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>796</v>
+      </c>
+      <c r="B2" t="s">
+        <v>797</v>
+      </c>
+      <c r="C2" t="s">
+        <v>798</v>
+      </c>
+      <c r="D2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F2" t="s">
+        <v>799</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>801</v>
+      </c>
+      <c r="B3" t="s">
+        <v>802</v>
+      </c>
+      <c r="C3" t="s">
+        <v>803</v>
+      </c>
+      <c r="D3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F3" t="s">
+        <v>804</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>806</v>
+      </c>
+      <c r="B4" t="s">
+        <v>807</v>
+      </c>
+      <c r="C4" t="s">
+        <v>808</v>
+      </c>
+      <c r="D4" t="s">
+        <v>172</v>
+      </c>
+      <c r="E4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F4" t="s">
+        <v>799</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>810</v>
+      </c>
+      <c r="B5" t="s">
+        <v>811</v>
+      </c>
+      <c r="C5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D5" t="s">
+        <v>172</v>
+      </c>
+      <c r="E5" t="s">
+        <v>172</v>
+      </c>
+      <c r="F5" t="s">
+        <v>812</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>814</v>
+      </c>
+      <c r="B6" t="s">
+        <v>815</v>
+      </c>
+      <c r="C6" t="s">
+        <v>199</v>
+      </c>
+      <c r="D6" t="s">
+        <v>172</v>
+      </c>
+      <c r="E6" t="s">
+        <v>172</v>
+      </c>
+      <c r="F6" t="s">
+        <v>812</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>817</v>
+      </c>
+      <c r="B7" t="s">
+        <v>818</v>
+      </c>
+      <c r="C7" t="s">
+        <v>819</v>
+      </c>
+      <c r="D7" t="s">
+        <v>172</v>
+      </c>
+      <c r="E7" t="s">
+        <v>172</v>
+      </c>
+      <c r="F7" t="s">
+        <v>431</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>821</v>
+      </c>
+      <c r="B8" t="s">
+        <v>822</v>
+      </c>
+      <c r="C8" t="s">
+        <v>823</v>
+      </c>
+      <c r="D8" t="s">
+        <v>172</v>
+      </c>
+      <c r="E8" t="s">
+        <v>172</v>
+      </c>
+      <c r="F8" t="s">
+        <v>799</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>825</v>
+      </c>
+      <c r="B9" t="s">
+        <v>826</v>
+      </c>
+      <c r="C9" t="s">
+        <v>827</v>
+      </c>
+      <c r="D9" t="s">
+        <v>172</v>
+      </c>
+      <c r="E9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F9" t="s">
+        <v>799</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>829</v>
+      </c>
+      <c r="B10" t="s">
+        <v>830</v>
+      </c>
+      <c r="C10" t="s">
+        <v>831</v>
+      </c>
+      <c r="D10" t="s">
+        <v>172</v>
+      </c>
+      <c r="E10" t="s">
+        <v>172</v>
+      </c>
+      <c r="F10" t="s">
+        <v>799</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>833</v>
+      </c>
+      <c r="B11" t="s">
+        <v>834</v>
+      </c>
+      <c r="C11" t="s">
+        <v>835</v>
+      </c>
+      <c r="D11" t="s">
+        <v>172</v>
+      </c>
+      <c r="E11" t="s">
+        <v>172</v>
+      </c>
+      <c r="F11" t="s">
+        <v>799</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>837</v>
+      </c>
+      <c r="B12" t="s">
+        <v>838</v>
+      </c>
+      <c r="C12" t="s">
+        <v>839</v>
+      </c>
+      <c r="D12" t="s">
+        <v>172</v>
+      </c>
+      <c r="E12" t="s">
+        <v>172</v>
+      </c>
+      <c r="F12" t="s">
+        <v>799</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>841</v>
+      </c>
+      <c r="B13" t="s">
+        <v>842</v>
+      </c>
+      <c r="C13" t="s">
+        <v>843</v>
+      </c>
+      <c r="D13" t="s">
+        <v>172</v>
+      </c>
+      <c r="E13" t="s">
+        <v>172</v>
+      </c>
+      <c r="F13" t="s">
+        <v>799</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>845</v>
+      </c>
+      <c r="B14" t="s">
+        <v>846</v>
+      </c>
+      <c r="C14" t="s">
+        <v>847</v>
+      </c>
+      <c r="D14" t="s">
+        <v>172</v>
+      </c>
+      <c r="E14" t="s">
+        <v>172</v>
+      </c>
+      <c r="F14" t="s">
+        <v>812</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>849</v>
+      </c>
+      <c r="B15" t="s">
+        <v>850</v>
+      </c>
+      <c r="C15" t="s">
+        <v>851</v>
+      </c>
+      <c r="D15" t="s">
+        <v>172</v>
+      </c>
+      <c r="E15" t="s">
+        <v>172</v>
+      </c>
+      <c r="F15" t="s">
+        <v>804</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>853</v>
+      </c>
+      <c r="B16" t="s">
+        <v>854</v>
+      </c>
+      <c r="C16" t="s">
+        <v>855</v>
+      </c>
+      <c r="D16" t="s">
+        <v>172</v>
+      </c>
+      <c r="E16" t="s">
+        <v>172</v>
+      </c>
+      <c r="F16" t="s">
+        <v>799</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>857</v>
+      </c>
+      <c r="B17" t="s">
+        <v>858</v>
+      </c>
+      <c r="C17" t="s">
+        <v>188</v>
+      </c>
+      <c r="D17" t="s">
+        <v>172</v>
+      </c>
+      <c r="E17" t="s">
+        <v>172</v>
+      </c>
+      <c r="F17" t="s">
+        <v>859</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>861</v>
+      </c>
+      <c r="B18" t="s">
+        <v>862</v>
+      </c>
+      <c r="C18" t="s">
+        <v>863</v>
+      </c>
+      <c r="D18" t="s">
+        <v>172</v>
+      </c>
+      <c r="E18" t="s">
+        <v>172</v>
+      </c>
+      <c r="F18" t="s">
+        <v>864</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>866</v>
+      </c>
+      <c r="B19" t="s">
+        <v>867</v>
+      </c>
+      <c r="C19" t="s">
+        <v>868</v>
+      </c>
+      <c r="D19" t="s">
+        <v>172</v>
+      </c>
+      <c r="E19" t="s">
+        <v>172</v>
+      </c>
+      <c r="F19" t="s">
+        <v>804</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>870</v>
+      </c>
+      <c r="B20" t="s">
+        <v>871</v>
+      </c>
+      <c r="C20" t="s">
+        <v>872</v>
+      </c>
+      <c r="D20" t="s">
+        <v>172</v>
+      </c>
+      <c r="E20" t="s">
+        <v>172</v>
+      </c>
+      <c r="F20" t="s">
+        <v>799</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>874</v>
+      </c>
+      <c r="B21" t="s">
+        <v>875</v>
+      </c>
+      <c r="C21" t="s">
+        <v>876</v>
+      </c>
+      <c r="D21" t="s">
+        <v>172</v>
+      </c>
+      <c r="E21" t="s">
+        <v>172</v>
+      </c>
+      <c r="F21" t="s">
+        <v>431</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>878</v>
+      </c>
+      <c r="B22" t="s">
+        <v>879</v>
+      </c>
+      <c r="C22" t="s">
+        <v>880</v>
+      </c>
+      <c r="D22" t="s">
+        <v>172</v>
+      </c>
+      <c r="E22" t="s">
+        <v>172</v>
+      </c>
+      <c r="F22" t="s">
+        <v>799</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>882</v>
+      </c>
+      <c r="B23" t="s">
+        <v>883</v>
+      </c>
+      <c r="C23" t="s">
+        <v>884</v>
+      </c>
+      <c r="D23" t="s">
+        <v>172</v>
+      </c>
+      <c r="E23" t="s">
+        <v>172</v>
+      </c>
+      <c r="F23" t="s">
+        <v>799</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>886</v>
+      </c>
+      <c r="B24" t="s">
+        <v>887</v>
+      </c>
+      <c r="C24" t="s">
+        <v>888</v>
+      </c>
+      <c r="D24" t="s">
+        <v>172</v>
+      </c>
+      <c r="E24" t="s">
+        <v>172</v>
+      </c>
+      <c r="F24" t="s">
+        <v>804</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>890</v>
+      </c>
+      <c r="B25" t="s">
+        <v>891</v>
+      </c>
+      <c r="C25" t="s">
+        <v>892</v>
+      </c>
+      <c r="D25" t="s">
+        <v>172</v>
+      </c>
+      <c r="E25" t="s">
+        <v>172</v>
+      </c>
+      <c r="F25" t="s">
+        <v>804</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>894</v>
+      </c>
+      <c r="B26" t="s">
+        <v>895</v>
+      </c>
+      <c r="C26" t="s">
+        <v>896</v>
+      </c>
+      <c r="D26" t="s">
+        <v>172</v>
+      </c>
+      <c r="E26" t="s">
+        <v>172</v>
+      </c>
+      <c r="F26" t="s">
+        <v>799</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>898</v>
+      </c>
+      <c r="B27" t="s">
+        <v>899</v>
+      </c>
+      <c r="C27" t="s">
+        <v>900</v>
+      </c>
+      <c r="D27" t="s">
+        <v>172</v>
+      </c>
+      <c r="E27" t="s">
+        <v>172</v>
+      </c>
+      <c r="F27" t="s">
+        <v>812</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>902</v>
+      </c>
+      <c r="B28" t="s">
+        <v>802</v>
+      </c>
+      <c r="C28" t="s">
+        <v>803</v>
+      </c>
+      <c r="D28" t="s">
+        <v>172</v>
+      </c>
+      <c r="E28" t="s">
+        <v>172</v>
+      </c>
+      <c r="F28" t="s">
+        <v>812</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>904</v>
+      </c>
+      <c r="B29" t="s">
+        <v>905</v>
+      </c>
+      <c r="C29" t="s">
+        <v>906</v>
+      </c>
+      <c r="D29" t="s">
+        <v>172</v>
+      </c>
+      <c r="E29" t="s">
+        <v>172</v>
+      </c>
+      <c r="F29" t="s">
+        <v>907</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>909</v>
+      </c>
+      <c r="B30" t="s">
+        <v>910</v>
+      </c>
+      <c r="C30" t="s">
+        <v>911</v>
+      </c>
+      <c r="D30" t="s">
+        <v>172</v>
+      </c>
+      <c r="E30" t="s">
+        <v>172</v>
+      </c>
+      <c r="F30" t="s">
+        <v>907</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>913</v>
+      </c>
+      <c r="B31" t="s">
+        <v>914</v>
+      </c>
+      <c r="C31" t="s">
+        <v>915</v>
+      </c>
+      <c r="D31" t="s">
+        <v>172</v>
+      </c>
+      <c r="E31" t="s">
+        <v>172</v>
+      </c>
+      <c r="F31" t="s">
+        <v>859</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>917</v>
+      </c>
+      <c r="B32" t="s">
+        <v>918</v>
+      </c>
+      <c r="C32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D32" t="s">
+        <v>172</v>
+      </c>
+      <c r="E32" t="s">
+        <v>172</v>
+      </c>
+      <c r="F32" t="s">
+        <v>281</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>921</v>
+      </c>
+      <c r="B33" t="s">
+        <v>922</v>
+      </c>
+      <c r="C33" t="s">
+        <v>923</v>
+      </c>
+      <c r="D33" t="s">
+        <v>172</v>
+      </c>
+      <c r="E33" t="s">
+        <v>172</v>
+      </c>
+      <c r="F33" t="s">
+        <v>431</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>925</v>
+      </c>
+      <c r="B34" t="s">
+        <v>926</v>
+      </c>
+      <c r="C34" t="s">
+        <v>927</v>
+      </c>
+      <c r="D34" t="s">
+        <v>172</v>
+      </c>
+      <c r="E34" t="s">
+        <v>172</v>
+      </c>
+      <c r="F34" t="s">
+        <v>799</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>929</v>
+      </c>
+      <c r="B35" t="s">
+        <v>930</v>
+      </c>
+      <c r="C35" t="s">
+        <v>931</v>
+      </c>
+      <c r="D35" t="s">
+        <v>172</v>
+      </c>
+      <c r="E35" t="s">
+        <v>172</v>
+      </c>
+      <c r="F35" t="s">
+        <v>932</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>934</v>
+      </c>
+      <c r="B36" t="s">
+        <v>935</v>
+      </c>
+      <c r="C36" t="s">
+        <v>936</v>
+      </c>
+      <c r="D36" t="s">
+        <v>172</v>
+      </c>
+      <c r="E36" t="s">
+        <v>172</v>
+      </c>
+      <c r="F36" t="s">
+        <v>907</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>934</v>
+      </c>
+      <c r="B37" t="s">
+        <v>826</v>
+      </c>
+      <c r="C37" t="s">
+        <v>827</v>
+      </c>
+      <c r="D37" t="s">
+        <v>172</v>
+      </c>
+      <c r="E37" t="s">
+        <v>172</v>
+      </c>
+      <c r="F37" t="s">
+        <v>907</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>939</v>
+      </c>
+      <c r="B38" t="s">
+        <v>940</v>
+      </c>
+      <c r="C38" t="s">
+        <v>941</v>
+      </c>
+      <c r="D38" t="s">
+        <v>172</v>
+      </c>
+      <c r="E38" t="s">
+        <v>172</v>
+      </c>
+      <c r="F38" t="s">
+        <v>799</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>943</v>
+      </c>
+      <c r="B39" t="s">
+        <v>944</v>
+      </c>
+      <c r="C39" t="s">
+        <v>945</v>
+      </c>
+      <c r="D39" t="s">
+        <v>172</v>
+      </c>
+      <c r="E39" t="s">
+        <v>172</v>
+      </c>
+      <c r="F39" t="s">
+        <v>799</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>947</v>
+      </c>
+      <c r="B40" t="s">
+        <v>948</v>
+      </c>
+      <c r="C40" t="s">
+        <v>936</v>
+      </c>
+      <c r="D40" t="s">
+        <v>172</v>
+      </c>
+      <c r="E40" t="s">
+        <v>172</v>
+      </c>
+      <c r="F40" t="s">
+        <v>804</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>950</v>
+      </c>
+      <c r="B41" t="s">
+        <v>951</v>
+      </c>
+      <c r="C41" t="s">
+        <v>936</v>
+      </c>
+      <c r="D41" t="s">
+        <v>172</v>
+      </c>
+      <c r="E41" t="s">
+        <v>172</v>
+      </c>
+      <c r="F41" t="s">
+        <v>804</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>953</v>
+      </c>
+      <c r="B42" t="s">
+        <v>954</v>
+      </c>
+      <c r="C42" t="s">
+        <v>955</v>
+      </c>
+      <c r="D42" t="s">
+        <v>172</v>
+      </c>
+      <c r="E42" t="s">
+        <v>172</v>
+      </c>
+      <c r="F42" t="s">
+        <v>799</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>957</v>
+      </c>
+      <c r="B43" t="s">
+        <v>958</v>
+      </c>
+      <c r="C43" t="s">
+        <v>931</v>
+      </c>
+      <c r="D43" t="s">
+        <v>172</v>
+      </c>
+      <c r="E43" t="s">
+        <v>172</v>
+      </c>
+      <c r="F43" t="s">
+        <v>932</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>957</v>
+      </c>
+      <c r="B44" t="s">
+        <v>960</v>
+      </c>
+      <c r="C44" t="s">
+        <v>931</v>
+      </c>
+      <c r="D44" t="s">
+        <v>172</v>
+      </c>
+      <c r="E44" t="s">
+        <v>172</v>
+      </c>
+      <c r="F44" t="s">
+        <v>932</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>962</v>
+      </c>
+      <c r="B45" t="s">
+        <v>963</v>
+      </c>
+      <c r="C45" t="s">
+        <v>427</v>
+      </c>
+      <c r="D45" t="s">
+        <v>172</v>
+      </c>
+      <c r="E45" t="s">
+        <v>172</v>
+      </c>
+      <c r="F45" t="s">
+        <v>799</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>964</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-09-29.xlsx
+++ b/docs/xlsx/jobs-2026-09-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="965">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1488" uniqueCount="966">
   <si>
     <t>Title</t>
   </si>
@@ -2390,6 +2390,9 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/7025e1eff0814a60b9607833db1f7f8c-west-region-program-manager-senior-program-manager-partners-for-justice-new-york</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7025e1eff0814a60b9607833db1f7f8c-west-region-program-manager-senior-program-manager-partners-for-justice-los-angeles</t>
   </si>
   <si>
     <t>Youth Organizer</t>
@@ -4112,7 +4115,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H134"/>
+  <dimension ref="A1:H135"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -7189,25 +7192,48 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>788</v>
+      </c>
+      <c r="B134" t="s">
+        <v>664</v>
+      </c>
+      <c r="C134" t="s">
+        <v>789</v>
+      </c>
+      <c r="D134" t="s">
+        <v>171</v>
+      </c>
+      <c r="E134" t="s">
+        <v>790</v>
+      </c>
+      <c r="F134" t="s">
+        <v>666</v>
+      </c>
+      <c r="H134" s="2" t="s">
         <v>792</v>
       </c>
-      <c r="B134" t="s">
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
         <v>793</v>
       </c>
-      <c r="C134" t="s">
+      <c r="B135" t="s">
+        <v>794</v>
+      </c>
+      <c r="C135" t="s">
         <v>374</v>
       </c>
-      <c r="D134" t="s">
-        <v>171</v>
-      </c>
-      <c r="E134" t="s">
-        <v>794</v>
-      </c>
-      <c r="F134" t="s">
+      <c r="D135" t="s">
+        <v>171</v>
+      </c>
+      <c r="E135" t="s">
+        <v>795</v>
+      </c>
+      <c r="F135" t="s">
         <v>484</v>
       </c>
-      <c r="H134" s="2" t="s">
-        <v>795</v>
+      <c r="H135" s="2" t="s">
+        <v>796</v>
       </c>
     </row>
   </sheetData>
@@ -7346,6 +7372,7 @@
     <hyperlink ref="H132" r:id="rId131"/>
     <hyperlink ref="H133" r:id="rId132"/>
     <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -7395,13 +7422,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B2" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C2" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D2" t="s">
         <v>172</v>
@@ -7410,21 +7437,21 @@
         <v>172</v>
       </c>
       <c r="F2" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B3" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D3" t="s">
         <v>172</v>
@@ -7433,21 +7460,21 @@
         <v>172</v>
       </c>
       <c r="F3" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B4" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C4" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D4" t="s">
         <v>172</v>
@@ -7456,18 +7483,18 @@
         <v>172</v>
       </c>
       <c r="F4" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B5" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C5" t="s">
         <v>199</v>
@@ -7479,18 +7506,18 @@
         <v>172</v>
       </c>
       <c r="F5" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B6" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C6" t="s">
         <v>199</v>
@@ -7502,21 +7529,21 @@
         <v>172</v>
       </c>
       <c r="F6" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B7" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C7" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D7" t="s">
         <v>172</v>
@@ -7528,18 +7555,18 @@
         <v>431</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B8" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C8" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D8" t="s">
         <v>172</v>
@@ -7548,21 +7575,21 @@
         <v>172</v>
       </c>
       <c r="F8" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B9" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C9" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D9" t="s">
         <v>172</v>
@@ -7571,21 +7598,21 @@
         <v>172</v>
       </c>
       <c r="F9" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B10" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C10" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D10" t="s">
         <v>172</v>
@@ -7594,21 +7621,21 @@
         <v>172</v>
       </c>
       <c r="F10" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B11" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C11" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D11" t="s">
         <v>172</v>
@@ -7617,21 +7644,21 @@
         <v>172</v>
       </c>
       <c r="F11" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B12" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C12" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D12" t="s">
         <v>172</v>
@@ -7640,21 +7667,21 @@
         <v>172</v>
       </c>
       <c r="F12" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B13" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C13" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D13" t="s">
         <v>172</v>
@@ -7663,21 +7690,21 @@
         <v>172</v>
       </c>
       <c r="F13" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B14" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C14" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D14" t="s">
         <v>172</v>
@@ -7686,21 +7713,21 @@
         <v>172</v>
       </c>
       <c r="F14" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B15" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C15" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D15" t="s">
         <v>172</v>
@@ -7709,21 +7736,21 @@
         <v>172</v>
       </c>
       <c r="F15" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B16" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C16" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D16" t="s">
         <v>172</v>
@@ -7732,18 +7759,18 @@
         <v>172</v>
       </c>
       <c r="F16" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B17" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C17" t="s">
         <v>188</v>
@@ -7755,21 +7782,21 @@
         <v>172</v>
       </c>
       <c r="F17" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B18" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C18" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D18" t="s">
         <v>172</v>
@@ -7778,21 +7805,21 @@
         <v>172</v>
       </c>
       <c r="F18" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B19" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C19" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D19" t="s">
         <v>172</v>
@@ -7801,21 +7828,21 @@
         <v>172</v>
       </c>
       <c r="F19" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B20" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C20" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D20" t="s">
         <v>172</v>
@@ -7824,21 +7851,21 @@
         <v>172</v>
       </c>
       <c r="F20" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B21" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C21" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="D21" t="s">
         <v>172</v>
@@ -7850,18 +7877,18 @@
         <v>431</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B22" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C22" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="D22" t="s">
         <v>172</v>
@@ -7870,21 +7897,21 @@
         <v>172</v>
       </c>
       <c r="F22" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B23" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C23" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D23" t="s">
         <v>172</v>
@@ -7893,21 +7920,21 @@
         <v>172</v>
       </c>
       <c r="F23" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B24" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C24" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="D24" t="s">
         <v>172</v>
@@ -7916,21 +7943,21 @@
         <v>172</v>
       </c>
       <c r="F24" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B25" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C25" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D25" t="s">
         <v>172</v>
@@ -7939,21 +7966,21 @@
         <v>172</v>
       </c>
       <c r="F25" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B26" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C26" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D26" t="s">
         <v>172</v>
@@ -7962,21 +7989,21 @@
         <v>172</v>
       </c>
       <c r="F26" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B27" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C27" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="D27" t="s">
         <v>172</v>
@@ -7985,21 +8012,21 @@
         <v>172</v>
       </c>
       <c r="F27" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B28" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C28" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D28" t="s">
         <v>172</v>
@@ -8008,21 +8035,21 @@
         <v>172</v>
       </c>
       <c r="F28" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B29" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C29" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D29" t="s">
         <v>172</v>
@@ -8031,21 +8058,21 @@
         <v>172</v>
       </c>
       <c r="F29" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B30" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C30" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="D30" t="s">
         <v>172</v>
@@ -8054,21 +8081,21 @@
         <v>172</v>
       </c>
       <c r="F30" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B31" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C31" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D31" t="s">
         <v>172</v>
@@ -8077,21 +8104,21 @@
         <v>172</v>
       </c>
       <c r="F31" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B32" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C32" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="D32" t="s">
         <v>172</v>
@@ -8103,18 +8130,18 @@
         <v>281</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B33" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C33" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D33" t="s">
         <v>172</v>
@@ -8126,18 +8153,18 @@
         <v>431</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B34" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="C34" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D34" t="s">
         <v>172</v>
@@ -8146,21 +8173,21 @@
         <v>172</v>
       </c>
       <c r="F34" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B35" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C35" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D35" t="s">
         <v>172</v>
@@ -8169,21 +8196,21 @@
         <v>172</v>
       </c>
       <c r="F35" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B36" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C36" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="D36" t="s">
         <v>172</v>
@@ -8192,21 +8219,21 @@
         <v>172</v>
       </c>
       <c r="F36" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B37" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C37" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D37" t="s">
         <v>172</v>
@@ -8215,21 +8242,21 @@
         <v>172</v>
       </c>
       <c r="F37" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B38" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C38" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="D38" t="s">
         <v>172</v>
@@ -8238,21 +8265,21 @@
         <v>172</v>
       </c>
       <c r="F38" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B39" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C39" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="D39" t="s">
         <v>172</v>
@@ -8261,21 +8288,21 @@
         <v>172</v>
       </c>
       <c r="F39" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B40" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C40" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="D40" t="s">
         <v>172</v>
@@ -8284,21 +8311,21 @@
         <v>172</v>
       </c>
       <c r="F40" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B41" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C41" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="D41" t="s">
         <v>172</v>
@@ -8307,21 +8334,21 @@
         <v>172</v>
       </c>
       <c r="F41" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B42" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C42" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="D42" t="s">
         <v>172</v>
@@ -8330,21 +8357,21 @@
         <v>172</v>
       </c>
       <c r="F42" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B43" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C43" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D43" t="s">
         <v>172</v>
@@ -8353,21 +8380,21 @@
         <v>172</v>
       </c>
       <c r="F43" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B44" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C44" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D44" t="s">
         <v>172</v>
@@ -8376,18 +8403,18 @@
         <v>172</v>
       </c>
       <c r="F44" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B45" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C45" t="s">
         <v>427</v>
@@ -8399,10 +8426,10 @@
         <v>172</v>
       </c>
       <c r="F45" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
   </sheetData>
